--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teama\Desktop\SizzleEnglishMain\ShivSizllingZuiq\UserScore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEF0440-F8D5-41EC-BEAA-945568CF5461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDE720B-DB55-47E6-A261-683AEE30948D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2925,6 +2925,9 @@
       <c r="F18" t="s">
         <v>91</v>
       </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
@@ -2945,6 +2948,9 @@
       <c r="F19" t="s">
         <v>96</v>
       </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
@@ -2964,6 +2970,9 @@
       </c>
       <c r="F20" t="s">
         <v>101</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teama\Desktop\SizzleEnglishMain\ShivSizllingZuiq\UserScore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDE720B-DB55-47E6-A261-683AEE30948D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1F45E7-96F2-42BC-82BA-83BF5FAB4ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2994,6 +2994,9 @@
       <c r="F21" t="s">
         <v>106</v>
       </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
@@ -3014,6 +3017,9 @@
       <c r="F22" t="s">
         <v>111</v>
       </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
@@ -3034,6 +3040,9 @@
       <c r="F23" t="s">
         <v>116</v>
       </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
@@ -3054,6 +3063,9 @@
       <c r="F24" t="s">
         <v>121</v>
       </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
@@ -3074,6 +3086,9 @@
       <c r="F25" t="s">
         <v>126</v>
       </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
@@ -3094,6 +3109,9 @@
       <c r="F26" t="s">
         <v>131</v>
       </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -3114,6 +3132,9 @@
       <c r="F27" t="s">
         <v>136</v>
       </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
@@ -3134,6 +3155,9 @@
       <c r="F28" t="s">
         <v>141</v>
       </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
@@ -3154,6 +3178,9 @@
       <c r="F29" t="s">
         <v>146</v>
       </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
@@ -3174,6 +3201,9 @@
       <c r="F30" t="s">
         <v>151</v>
       </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
@@ -3194,6 +3224,9 @@
       <c r="F31" t="s">
         <v>156</v>
       </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
@@ -3214,8 +3247,11 @@
       <c r="F32" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3234,8 +3270,11 @@
       <c r="F33" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3254,8 +3293,11 @@
       <c r="F34" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3274,8 +3316,11 @@
       <c r="F35" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3294,8 +3339,11 @@
       <c r="F36" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3314,8 +3362,11 @@
       <c r="F37" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3334,8 +3385,11 @@
       <c r="F38" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3354,8 +3408,11 @@
       <c r="F39" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3374,8 +3431,11 @@
       <c r="F40" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3394,8 +3454,11 @@
       <c r="F41" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3415,7 +3478,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3435,7 +3498,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3455,7 +3518,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3475,7 +3538,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3495,7 +3558,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3515,7 +3578,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teama\Desktop\SizzleEnglishMain\ShivSizllingZuiq\UserScore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1F45E7-96F2-42BC-82BA-83BF5FAB4ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A178FBD9-0D6B-438C-9B43-28A994B963D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3477,6 +3477,9 @@
       <c r="F42" t="s">
         <v>210</v>
       </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
@@ -3497,6 +3500,9 @@
       <c r="F43" t="s">
         <v>215</v>
       </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
@@ -3517,6 +3523,9 @@
       <c r="F44" t="s">
         <v>220</v>
       </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
@@ -3537,6 +3546,9 @@
       <c r="F45" t="s">
         <v>225</v>
       </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
@@ -3557,6 +3569,9 @@
       <c r="F46" t="s">
         <v>230</v>
       </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
@@ -3577,6 +3592,9 @@
       <c r="F47" t="s">
         <v>235</v>
       </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
@@ -3597,8 +3615,11 @@
       <c r="F48" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3617,8 +3638,11 @@
       <c r="F49" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3637,8 +3661,11 @@
       <c r="F50" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3657,8 +3684,11 @@
       <c r="F51" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3677,8 +3707,11 @@
       <c r="F52" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3697,8 +3730,11 @@
       <c r="F53" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3717,8 +3753,11 @@
       <c r="F54" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3737,8 +3776,11 @@
       <c r="F55" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3757,8 +3799,11 @@
       <c r="F56" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3777,8 +3822,11 @@
       <c r="F57" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3797,8 +3845,11 @@
       <c r="F58" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3817,8 +3868,11 @@
       <c r="F59" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3837,8 +3891,11 @@
       <c r="F60" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3857,8 +3914,11 @@
       <c r="F61" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3877,8 +3937,11 @@
       <c r="F62" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3897,8 +3960,11 @@
       <c r="F63" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3917,8 +3983,11 @@
       <c r="F64" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3937,8 +4006,11 @@
       <c r="F65" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3957,8 +4029,11 @@
       <c r="F66" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3977,8 +4052,11 @@
       <c r="F67" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3997,8 +4075,11 @@
       <c r="F68" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4018,7 +4099,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4038,7 +4119,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4058,7 +4139,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4078,7 +4159,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4098,7 +4179,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4118,7 +4199,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4138,7 +4219,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4158,7 +4239,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4178,7 +4259,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4198,7 +4279,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4218,7 +4299,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teama\Desktop\SizzleEnglishMain\ShivSizllingZuiq\UserScore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A178FBD9-0D6B-438C-9B43-28A994B963D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E2B585-D1C0-4CCE-928E-5C835AA3F9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4098,6 +4098,9 @@
       <c r="F69" t="s">
         <v>345</v>
       </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Resilience </t>
+          <t xml:space="preserve"> Alacrity </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The ability to recover quickly from difficulties </t>
+          <t xml:space="preserve"> cheerful willingness </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> toughness, endurance, grit </t>
+          <t xml:space="preserve"> eagerness, enthusiasm </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> weakness, fragility </t>
+          <t xml:space="preserve"> reluctance, hesitation </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She showed resilience after failing the exam.  </t>
+          <t xml:space="preserve"> She accepted the job offer with alacrity.</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -504,27 +504,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Elated </t>
+          <t xml:space="preserve"> Ambivalent </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Extremely happy or joyful </t>
+          <t xml:space="preserve"> having mixed feelings </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> thrilled, overjoyed, ecstatic </t>
+          <t xml:space="preserve"> uncertain, doubtful </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> depressed, sorrowful </t>
+          <t xml:space="preserve"> definite, certain </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He was elated after winning the match.  </t>
+          <t xml:space="preserve"> He felt ambivalent about changing his career.</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -537,32 +537,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Diligent </t>
+          <t xml:space="preserve"> Anomaly </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Showing persistent and hard-working effort </t>
+          <t xml:space="preserve"> something unusual or abnormal </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> industrious, hardworking, attentive </t>
+          <t xml:space="preserve"> irregularity, deviation </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> lazy, careless </t>
+          <t xml:space="preserve"> norm, standard </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She is a diligent student who never misses homework.  </t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Scientists studied the climate anomaly carefully.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -570,32 +568,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Serene </t>
+          <t xml:space="preserve"> Apathy </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Calm and peaceful </t>
+          <t xml:space="preserve"> lack of interest or concern </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tranquil, composed, placid </t>
+          <t xml:space="preserve"> indifference, unconcern </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> agitated, chaotic </t>
+          <t xml:space="preserve"> enthusiasm, passion </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The lake looked serene under the moonlight.  </t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The voters’ apathy affected the election turnout.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -603,32 +599,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Frugal </t>
+          <t xml:space="preserve"> Arduous </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Economical in spending or resources </t>
+          <t xml:space="preserve"> requiring great effort </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> thrifty, economical, prudent </t>
+          <t xml:space="preserve"> difficult, strenuous </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> wasteful, extravagant </t>
+          <t xml:space="preserve"> easy, effortless </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He lived a frugal life despite his wealth.  </t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Preparing for IELTS can be an arduous task.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -636,32 +630,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Amiable </t>
+          <t xml:space="preserve"> Astounding </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Friendly and pleasant </t>
+          <t xml:space="preserve"> surprisingly impressive or notable </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> genial, cordial, likable </t>
+          <t xml:space="preserve"> astonishing, remarkable </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rude, hostile </t>
+          <t xml:space="preserve"> ordinary, unimpressive </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The teacher was very amiable and helpful.  </t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Her progress in English was astounding.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -669,32 +661,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Candid </t>
+          <t xml:space="preserve"> Austere </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Honest and straightforward </t>
+          <t xml:space="preserve"> simple and without luxury </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> frank, open, blunt </t>
+          <t xml:space="preserve"> plain, severe </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dishonest, secretive </t>
+          <t xml:space="preserve"> luxurious, lavish </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She gave a candid opinion about the movie.  </t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The room was austere but very clean.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -702,32 +692,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Vivid </t>
+          <t xml:space="preserve"> Avarice </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Producing strong, clear images </t>
+          <t xml:space="preserve"> extreme greed for wealth </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> graphic, striking, intense </t>
+          <t xml:space="preserve"> greed, cupidity </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dull, faint </t>
+          <t xml:space="preserve"> generosity, charity </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The book gave a vivid description of the battle.  </t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His avarice led to unethical decisions.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -735,32 +723,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jubilant </t>
+          <t xml:space="preserve"> Belligerent </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feeling great happiness and joy </t>
+          <t xml:space="preserve"> hostile and aggressive </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ecstatic, delighted, thrilled </t>
+          <t xml:space="preserve"> aggressive, combative </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> gloomy, sad </t>
+          <t xml:space="preserve"> peaceful, friendly </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The fans were jubilant after the victory.  </t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His belligerent tone ended the conversation.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -768,32 +754,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lenient </t>
+          <t xml:space="preserve"> Benign </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tolerant and not strict </t>
+          <t xml:space="preserve"> kind and harmless </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> forgiving, permissive, soft </t>
+          <t xml:space="preserve"> gentle, harmless </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> harsh, severe </t>
+          <t xml:space="preserve"> harmful, dangerous </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The teacher was lenient with late submissions.  </t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The doctor confirmed the tumor was benign.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -801,32 +785,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tedious </t>
+          <t xml:space="preserve"> Bolster </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Long and boring </t>
+          <t xml:space="preserve"> support or strengthen </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> monotonous, tiresome, dull </t>
+          <t xml:space="preserve"> reinforce, support </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> exciting, lively </t>
+          <t xml:space="preserve"> weaken, undermine </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Typing the entire document was a tedious task.  </t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Extra examples can bolster your argument.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -834,32 +816,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Astute </t>
+          <t xml:space="preserve"> Candid </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Clever and perceptive </t>
+          <t xml:space="preserve"> honest and straightforward </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> shrewd, insightful, smart </t>
+          <t xml:space="preserve"> frank, sincere </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> naive, foolish </t>
+          <t xml:space="preserve"> deceitful, dishonest </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She made an astute business decision.  </t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> She gave a candid opinion about the project.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -867,32 +847,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Agile </t>
+          <t xml:space="preserve"> Capitulate </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quick and light in movement </t>
+          <t xml:space="preserve"> surrender or give in </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> nimble, quick, graceful </t>
+          <t xml:space="preserve"> yield, submit </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> clumsy, stiff </t>
+          <t xml:space="preserve"> resist, fight </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The cat was agile and jumped over the fence.  </t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The army had to capitulate after losing supplies.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -900,32 +878,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Benevolent </t>
+          <t xml:space="preserve"> Cogent </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Kind and charitable </t>
+          <t xml:space="preserve"> clear and convincing </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> compassionate, generous, kindhearted </t>
+          <t xml:space="preserve"> persuasive, compelling </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> malevolent, cruel </t>
+          <t xml:space="preserve"> weak, unconvincing </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The king was known for his benevolent rule.  </t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His cogent explanation convinced the class.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -933,32 +909,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hasty </t>
+          <t xml:space="preserve"> Cohesive </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Done with excessive speed </t>
+          <t xml:space="preserve"> sticking together well </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rushed, impulsive, reckless </t>
+          <t xml:space="preserve"> unified, connected </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> careful, thoughtful </t>
+          <t xml:space="preserve"> fragmented, disjointed </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He made a hasty decision without thinking.  </t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> A cohesive essay scores higher in IELTS writing.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -966,32 +940,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Skeptical </t>
+          <t xml:space="preserve"> Complacent </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Having doubts or reservations </t>
+          <t xml:space="preserve"> overly satisfied and unconcerned </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> doubtful, suspicious, hesitant </t>
+          <t xml:space="preserve"> self-satisfied, smug </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> trusting, certain </t>
+          <t xml:space="preserve"> concerned, dissatisfied </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She was skeptical about the offer.  </t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> He became complacent after small success.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -999,32 +971,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Gracious </t>
+          <t xml:space="preserve"> Conducive </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Kind and courteous </t>
+          <t xml:space="preserve"> making something likely to happen </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> polite, considerate, courteous </t>
+          <t xml:space="preserve"> favorable, helpful </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rude, harsh </t>
+          <t xml:space="preserve"> harmful, unfavorable </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He was gracious in defeat.  </t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Quiet study rooms are conducive to learning.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1032,32 +1002,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feeble </t>
+          <t xml:space="preserve"> Conundrum </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lacking physical strength </t>
+          <t xml:space="preserve"> confusing and difficult problem </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> weak, frail, delicate </t>
+          <t xml:space="preserve"> puzzle, dilemma </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> strong, powerful </t>
+          <t xml:space="preserve"> solution, answer </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The old man’s voice was feeble.  </t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Choosing a career became a conundrum for her.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1065,32 +1033,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Humble </t>
+          <t xml:space="preserve"> Credible </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Modest and not arrogant </t>
+          <t xml:space="preserve"> believable or trustworthy </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> unassuming, modest, meek </t>
+          <t xml:space="preserve"> reliable, plausible </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arrogant, boastful </t>
+          <t xml:space="preserve"> unbelievable, doubtful </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Despite his success, he remained humble.  </t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The witness gave a credible statement.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1098,32 +1064,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mundane </t>
+          <t xml:space="preserve"> Cryptic </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lacking interest or excitement </t>
+          <t xml:space="preserve"> mysterious or unclear </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dull, routine, ordinary </t>
+          <t xml:space="preserve"> obscure, puzzling </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> extraordinary, exciting </t>
+          <t xml:space="preserve"> clear, obvious </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He was bored with his mundane job.  </t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His cryptic message confused everyone.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1131,32 +1095,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impeccable </t>
+          <t xml:space="preserve"> Cynical </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Perfect and without fault </t>
+          <t xml:space="preserve"> distrustful of others’ motives </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> flawless, spotless, perfect </t>
+          <t xml:space="preserve"> skeptical, suspicious </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> flawed, imperfect </t>
+          <t xml:space="preserve"> trusting, naive </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Her performance was impeccable.  </t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Many people are cynical about politics.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1164,32 +1126,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Eloquent </t>
+          <t xml:space="preserve"> Daunting </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fluent and persuasive in speaking </t>
+          <t xml:space="preserve"> seeming difficult to handle </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> articulate, expressive, fluent </t>
+          <t xml:space="preserve"> intimidating, discouraging </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> inarticulate, dull </t>
+          <t xml:space="preserve"> encouraging, reassuring </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He gave an eloquent speech.  </t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Speaking in English can feel daunting at first.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1197,32 +1157,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arduous </t>
+          <t xml:space="preserve"> Debilitate </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Involving great effort </t>
+          <t xml:space="preserve"> to weaken severely </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> difficult, exhausting, strenuous </t>
+          <t xml:space="preserve"> weaken, disable </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> easy, simple </t>
+          <t xml:space="preserve"> strengthen, energize </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Climbing the mountain was an arduous task.  </t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The disease can debilitate elderly patients.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1230,32 +1188,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Naive </t>
+          <t xml:space="preserve"> Deference </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lacking experience or wisdom </t>
+          <t xml:space="preserve"> respectful submission </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> innocent, gullible, simple </t>
+          <t xml:space="preserve"> respect, regard </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> wise, experienced </t>
+          <t xml:space="preserve"> disrespect, contempt </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The child was naive to believe the story.  </t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Students showed deference to their teacher.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1263,32 +1219,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Valiant </t>
+          <t xml:space="preserve"> Deliberate </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Brave and courageous </t>
+          <t xml:space="preserve"> done with careful thought </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> heroic, fearless, bold </t>
+          <t xml:space="preserve"> intentional, planned </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> cowardly, timid </t>
+          <t xml:space="preserve"> accidental, unplanned </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The soldier made a valiant effort to save lives.  </t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His insult was deliberate, not accidental.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1296,32 +1250,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abundant </t>
+          <t xml:space="preserve"> Delineate </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Present in large quantities </t>
+          <t xml:space="preserve"> describe precisely </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> plentiful, ample, overflowing </t>
+          <t xml:space="preserve"> outline, define </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> scarce, limited </t>
+          <t xml:space="preserve"> confuse, obscure </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The region has abundant natural resources.  </t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The report delineates the new policy clearly.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1329,32 +1281,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Brisk </t>
+          <t xml:space="preserve"> Denounce </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quick and active </t>
+          <t xml:space="preserve"> publicly criticize </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> energetic, lively, rapid </t>
+          <t xml:space="preserve"> condemn, accuse </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> slow, sluggish </t>
+          <t xml:space="preserve"> praise, applaud </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She took a brisk walk in the morning.  </t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The leader denounced corruption strongly.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1362,32 +1312,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cautious </t>
+          <t xml:space="preserve"> Derive </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Careful to avoid danger or mistakes </t>
+          <t xml:space="preserve"> obtain from a source </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> careful, alert, vigilant </t>
+          <t xml:space="preserve"> obtain, extract </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> reckless, careless </t>
+          <t xml:space="preserve"> lose, forfeit </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He is always cautious while driving.  </t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Many English words are derived from Latin.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1395,32 +1343,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dauntless </t>
+          <t xml:space="preserve"> Detrimental </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Showing fearlessness and determination </t>
+          <t xml:space="preserve"> harmful or damaging </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fearless, bold, courageous </t>
+          <t xml:space="preserve"> harmful, adverse </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fearful, timid </t>
+          <t xml:space="preserve"> beneficial, helpful </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The dauntless explorer ventured into the jungle.  </t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Smoking is detrimental to health.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1428,32 +1374,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Eager </t>
+          <t xml:space="preserve"> Dichotomy </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Very interested or excited about something </t>
+          <t xml:space="preserve"> clear division into two parts </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> enthusiastic, keen, excited </t>
+          <t xml:space="preserve"> contrast, split </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> indifferent, uninterested </t>
+          <t xml:space="preserve"> unity, agreement </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She was eager to start her new job.  </t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The book explains the dichotomy between rich and poor.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1461,32 +1405,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feisty </t>
+          <t xml:space="preserve"> Didactic </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Energetic and determined </t>
+          <t xml:space="preserve"> intended to teach </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> spirited, lively, bold </t>
+          <t xml:space="preserve"> instructive, educational </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> timid, passive </t>
+          <t xml:space="preserve"> confusing, misleading </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The feisty puppy barked at the big dog.  </t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The story had a didactic moral lesson.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1494,32 +1436,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Gaudy </t>
+          <t xml:space="preserve"> Diligent </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Too brightly colored or showy </t>
+          <t xml:space="preserve"> showing hard work </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> flashy, flamboyant, loud </t>
+          <t xml:space="preserve"> hardworking, industrious </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> modest, plain </t>
+          <t xml:space="preserve"> lazy, careless </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He wore a gaudy shirt to the party.  </t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Diligent students usually achieve higher bands.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1527,32 +1467,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hinder </t>
+          <t xml:space="preserve"> Discreet </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To make it difficult to do something </t>
+          <t xml:space="preserve"> careful in speech or behavior </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> obstruct, block, delay </t>
+          <t xml:space="preserve"> cautious, tactful </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> help, aid </t>
+          <t xml:space="preserve"> careless, reckless </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The rain will hinder our travel plans.  </t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> She was discreet when discussing personal matters.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1560,32 +1498,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Illuminate </t>
+          <t xml:space="preserve"> Discrepancy </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To light up or make clear </t>
+          <t xml:space="preserve"> difference or inconsistency </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> brighten, clarify, reveal </t>
+          <t xml:space="preserve"> variation, mismatch </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> darken, confuse </t>
+          <t xml:space="preserve"> similarity, agreement </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The flashlight illuminated the path.  </t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> There was a discrepancy in the data.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1593,32 +1529,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jeopardy </t>
+          <t xml:space="preserve"> Disdain </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Danger of loss or harm </t>
+          <t xml:space="preserve"> feeling of contempt </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> risk, peril, threat </t>
+          <t xml:space="preserve"> scorn, contempt </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> safety, security </t>
+          <t xml:space="preserve"> respect, admiration </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His mistake put the mission in jeopardy.  </t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> He spoke with disdain about cheating.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1626,32 +1560,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Keen </t>
+          <t xml:space="preserve"> Disparage </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Highly developed or sharp </t>
+          <t xml:space="preserve"> criticize or belittle </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> sharp, acute, eager </t>
+          <t xml:space="preserve"> belittle, mock </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dull, indifferent </t>
+          <t xml:space="preserve"> praise, compliment </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She has a keen sense of smell.  </t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> He disparaged her ideas unfairly.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1659,32 +1591,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Linger </t>
+          <t xml:space="preserve"> Disseminate </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stay in a place longer than necessary </t>
+          <t xml:space="preserve"> spread widely </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> remain, stay, loiter </t>
+          <t xml:space="preserve"> distribute, circulate </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> leave, hurry </t>
+          <t xml:space="preserve"> conceal, hide </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He lingered after the meeting ended.  </t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Social media helps disseminate information.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1692,32 +1622,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Meek </t>
+          <t xml:space="preserve"> Divergent </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quiet and gentle </t>
+          <t xml:space="preserve"> differing from another </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> humble, timid, submissive </t>
+          <t xml:space="preserve"> different, varied </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> bold, assertive </t>
+          <t xml:space="preserve"> similar, identical </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The child was too meek to speak up.  </t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> They had divergent opinions on the issue.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1725,32 +1653,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nimble </t>
+          <t xml:space="preserve"> Docile </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quick and light in movement </t>
+          <t xml:space="preserve"> easy to control or manage </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> agile, swift, graceful </t>
+          <t xml:space="preserve"> obedient, submissive </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> clumsy, sluggish </t>
+          <t xml:space="preserve"> defiant, stubborn </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The gymnast was nimble on the beam.  </t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The dog was surprisingly docile.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1758,32 +1684,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Oblivious </t>
+          <t xml:space="preserve"> Dogmatic </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unaware or unconcerned </t>
+          <t xml:space="preserve"> asserting opinions rigidly </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ignorant, unaware, inattentive </t>
+          <t xml:space="preserve"> rigid, inflexible </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> aware, conscious </t>
+          <t xml:space="preserve"> flexible, open-minded </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He was oblivious to the noise around him.  </t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> He is dogmatic and never listens to others.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1791,32 +1715,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Perplexed </t>
+          <t xml:space="preserve"> Eccentric </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Confused or puzzled </t>
+          <t xml:space="preserve"> unusual and slightly strange </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> bewildered, baffled, confused </t>
+          <t xml:space="preserve"> odd, peculiar </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> clear, certain </t>
+          <t xml:space="preserve"> normal, conventional </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She looked perplexed by the riddle.  </t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His eccentric habits amused his friends.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1824,32 +1746,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quench </t>
+          <t xml:space="preserve"> Eclectic </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To satisfy or extinguish </t>
+          <t xml:space="preserve"> choosing from various sources </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> satisfy, extinguish, relieve </t>
+          <t xml:space="preserve"> diverse, varied </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ignite, provoke </t>
+          <t xml:space="preserve"> narrow, limited </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Water quenched his thirst.  </t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> She has an eclectic taste in music.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1857,32 +1777,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Radiant </t>
+          <t xml:space="preserve"> Egregious </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emitting light or joy </t>
+          <t xml:space="preserve"> extremely bad </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> glowing, shining, beaming </t>
+          <t xml:space="preserve"> shocking, outrageous </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dull, gloomy </t>
+          <t xml:space="preserve"> minor, slight </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Her face was radiant with happiness.  </t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The company made an egregious mistake.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1890,32 +1808,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sincere </t>
+          <t xml:space="preserve"> Elated </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genuine and honest </t>
+          <t xml:space="preserve"> extremely happy </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> honest, heartfelt, truthful </t>
+          <t xml:space="preserve"> overjoyed, delighted </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fake, insincere </t>
+          <t xml:space="preserve"> sad, depressed </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He gave a sincere apology.  </t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> She was elated after receiving the scholarship.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1923,32 +1839,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tame </t>
+          <t xml:space="preserve"> Elucidate </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not wild or dangerous </t>
+          <t xml:space="preserve"> make something clear </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> gentle, domesticated, calm </t>
+          <t xml:space="preserve"> explain, clarify </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> wild, fierce </t>
+          <t xml:space="preserve"> confuse, obscure </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The lion was surprisingly tame.  </t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The teacher elucidated the difficult topic.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1956,32 +1870,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unruly </t>
+          <t xml:space="preserve"> Emphatic </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Difficult to control </t>
+          <t xml:space="preserve"> showing emphasis </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> disobedient, wild, chaotic </t>
+          <t xml:space="preserve"> forceful, assertive </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> obedient, disciplined </t>
+          <t xml:space="preserve"> weak, hesitant </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The unruly class made teaching hard.  </t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> She gave an emphatic denial to the accusation.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1989,32 +1901,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Vast </t>
+          <t xml:space="preserve"> Empirical </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Very large in size or amount </t>
+          <t xml:space="preserve"> based on observation </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> immense, enormous, extensive </t>
+          <t xml:space="preserve"> experimental, factual </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tiny, limited </t>
+          <t xml:space="preserve"> theoretical, hypothetical </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The desert stretched into the vast distance.  </t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The conclusion is based on empirical data.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2022,32 +1932,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Weary </t>
+          <t xml:space="preserve"> Endorse </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Very tired or worn out </t>
+          <t xml:space="preserve"> publicly support </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> exhausted, fatigued, drained </t>
+          <t xml:space="preserve"> approve, back </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> energetic, fresh </t>
+          <t xml:space="preserve"> oppose, reject </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She felt weary after the long day.  </t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Many celebrities endorse products.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2055,32 +1963,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Yearn </t>
+          <t xml:space="preserve"> Engender </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To strongly desire something </t>
+          <t xml:space="preserve"> cause or produce </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> long, crave, desire </t>
+          <t xml:space="preserve"> generate, create </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dislike, hate </t>
+          <t xml:space="preserve"> stop, halt </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He yearned for his hometown.  </t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His speech engendered hope among the people.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2088,32 +1994,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zealous </t>
+          <t xml:space="preserve"> Enigmatic </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Full of enthusiasm and energy </t>
+          <t xml:space="preserve"> mysterious or puzzling </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> enthusiastic, passionate, fervent </t>
+          <t xml:space="preserve"> mysterious, cryptic </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> indifferent, apathetic </t>
+          <t xml:space="preserve"> clear, obvious </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The team was zealous about winning.  </t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His smile was enigmatic and unreadable.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2121,32 +2025,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abstruse </t>
+          <t xml:space="preserve"> Entice </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Difficult to understand </t>
+          <t xml:space="preserve"> attract by offering pleasure </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> obscure, complex, puzzling </t>
+          <t xml:space="preserve"> tempt, lure </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> simple, clear </t>
+          <t xml:space="preserve"> repel, discourage </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The professor's explanation was too abstruse for most students.  </t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Discounts are used to entice customers.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2154,32 +2056,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Belligerent </t>
+          <t xml:space="preserve"> Enumerate </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hostile and aggressive </t>
+          <t xml:space="preserve"> mention one by one </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> combative, antagonistic, warlike </t>
+          <t xml:space="preserve"> list, itemize </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> peaceful, friendly </t>
+          <t xml:space="preserve"> combine, merge </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His belligerent attitude caused tension in the room.  </t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The teacher enumerated the exam rules.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2187,32 +2087,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Capitulate </t>
+          <t xml:space="preserve"> Erratic </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To surrender or give in </t>
+          <t xml:space="preserve"> not regular or steady </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> yield, submit, concede </t>
+          <t xml:space="preserve"> unpredictable, irregular </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> resist, defend </t>
+          <t xml:space="preserve"> consistent, stable </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The enemy was forced to capitulate after the siege.  </t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His attendance was erratic throughout the term.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2220,32 +2118,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Debilitate </t>
+          <t xml:space="preserve"> Esoteric </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To weaken or drain strength </t>
+          <t xml:space="preserve"> understood by only a few </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> exhaust, impair, sap </t>
+          <t xml:space="preserve"> obscure, arcane </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> strengthen, energize </t>
+          <t xml:space="preserve"> common, familiar </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The long illness debilitated his body.  </t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The theory is too esoteric for beginners.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2253,32 +2149,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Enigmatic </t>
+          <t xml:space="preserve"> Exemplify </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mysterious or difficult to interpret </t>
+          <t xml:space="preserve"> show by example </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> puzzling, cryptic, obscure </t>
+          <t xml:space="preserve"> demonstrate, illustrate </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> obvious, clear </t>
+          <t xml:space="preserve"> misrepresent, distort </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Her enigmatic smile confused everyone.  </t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Her career exemplifies success through hard work.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2286,32 +2180,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fastidious </t>
+          <t xml:space="preserve"> Exorbitant </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Very attentive to detail </t>
+          <t xml:space="preserve"> unreasonably high </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> meticulous, fussy, picky </t>
+          <t xml:space="preserve"> excessive, extreme </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> careless, sloppy </t>
+          <t xml:space="preserve"> reasonable, moderate </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He is fastidious about keeping his desk clean.  </t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The rent prices in the city are exorbitant.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2319,32 +2211,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Garrulous </t>
+          <t xml:space="preserve"> Expeditious </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Excessively talkative </t>
+          <t xml:space="preserve"> done quickly and efficiently </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> chatty, verbose, talkative </t>
+          <t xml:space="preserve"> swift, rapid </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> quiet, reserved </t>
+          <t xml:space="preserve"> slow, delayed </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The garrulous host dominated the conversation.  </t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> He completed the task in an expeditious manner.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2352,32 +2242,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Harangue </t>
+          <t xml:space="preserve"> Fallacious </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A lengthy and aggressive speech </t>
+          <t xml:space="preserve"> based on false ideas </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tirade, rant, lecture </t>
+          <t xml:space="preserve"> misleading, incorrect </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> praise, silence </t>
+          <t xml:space="preserve"> correct, valid </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The manager gave a harsh harangue after the loss.  </t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The argument was fallacious and weak.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2385,32 +2273,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ineffable </t>
+          <t xml:space="preserve"> Feasible </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Too great to be expressed in words </t>
+          <t xml:space="preserve"> possible to do </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> indescribable, inexpressible, overwhelming </t>
+          <t xml:space="preserve"> practical, workable </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ordinary, expressible </t>
+          <t xml:space="preserve"> impossible, impractical </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The beauty of the sunset was ineffable.  </t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Your plan is feasible with enough funding.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2418,32 +2304,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Juxtapose </t>
+          <t xml:space="preserve"> Fervent </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To place side by side for comparison </t>
+          <t xml:space="preserve"> showing strong feeling </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> compare, contrast, align </t>
+          <t xml:space="preserve"> passionate, ardent </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> separate, divide </t>
+          <t xml:space="preserve"> indifferent, cold </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The artist juxtaposed light and dark colors effectively.  </t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> She is a fervent supporter of education for all.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2451,32 +2335,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Kowtow </t>
+          <t xml:space="preserve"> Flagrant </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To act in an excessively submissive manner </t>
+          <t xml:space="preserve"> obviously offensive </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> grovel, bow, fawn </t>
+          <t xml:space="preserve"> blatant, glaring </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> defy, resist </t>
+          <t xml:space="preserve"> minor, hidden </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He refused to kowtow to corrupt officials.  </t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> It was a flagrant violation of the rules.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2484,32 +2366,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lethargic </t>
+          <t xml:space="preserve"> Formidable </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lacking energy or enthusiasm </t>
+          <t xml:space="preserve"> inspiring fear or respect </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> sluggish, dull, lazy </t>
+          <t xml:space="preserve"> intimidating, powerful </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> active, energetic </t>
+          <t xml:space="preserve"> weak, harmless </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She felt lethargic after the heavy meal.  </t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> He is a formidable opponent in debate.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2517,32 +2397,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Magnanimous </t>
+          <t xml:space="preserve"> Frivolous </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Very generous or forgiving </t>
+          <t xml:space="preserve"> not serious or sensible </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> noble, kind, selfless </t>
+          <t xml:space="preserve"> trivial, silly </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> petty, selfish </t>
+          <t xml:space="preserve"> serious, important </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He was magnanimous in forgiving his rival.  </t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Stop spending money on frivolous things.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2550,32 +2428,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nebulous </t>
+          <t xml:space="preserve"> Futile </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Vague or unclear </t>
+          <t xml:space="preserve"> incapable of producing results </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> hazy, indistinct, blurred </t>
+          <t xml:space="preserve"> useless, pointless </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> clear, obvious </t>
+          <t xml:space="preserve"> effective, successful </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The plan was still too nebulous to follow.  </t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Their efforts to save the tree were futile.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2583,32 +2459,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obfuscate </t>
+          <t xml:space="preserve"> Garrulous </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To make something unclear or confusing </t>
+          <t xml:space="preserve"> excessively talkative </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> obscure, blur, confuse </t>
+          <t xml:space="preserve"> talkative, chatty </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> clarify, explain </t>
+          <t xml:space="preserve"> silent, quiet </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The politician tried to obfuscate the issue.  </t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> The garrulous man dominated the conversation.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2616,32 +2490,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pernicious </t>
+          <t xml:space="preserve"> Gaunt </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Harmful in a subtle way </t>
+          <t xml:space="preserve"> extremely thin </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> destructive, malicious, damaging </t>
+          <t xml:space="preserve"> skinny, emaciated </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> harmless, beneficial </t>
+          <t xml:space="preserve"> healthy, plump </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Social media can have a pernicious effect on teens.  </t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> After the illness, he looked gaunt.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2649,32 +2521,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quixotic </t>
+          <t xml:space="preserve"> Gregarious </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unrealistically idealistic </t>
+          <t xml:space="preserve"> sociable and outgoing </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dreamy, impractical, romantic </t>
+          <t xml:space="preserve"> sociable, friendly </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> realistic, pragmatic </t>
+          <t xml:space="preserve"> shy, introverted </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His quixotic plan was bound to fail.  </t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> She is gregarious and loves meeting new people.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2682,32 +2552,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Recalcitrant </t>
+          <t xml:space="preserve"> Hackneyed </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Resistant to authority or control </t>
+          <t xml:space="preserve"> overused and unoriginal </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> defiant, disobedient, uncooperative </t>
+          <t xml:space="preserve"> clichéd, stale </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> obedient, compliant </t>
+          <t xml:space="preserve"> fresh, original </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The recalcitrant student refused to follow rules.  </t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> His speech was full of hackneyed phrases.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2715,32 +2583,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sagacious </t>
+          <t xml:space="preserve"> Haphazard </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Wise and insightful </t>
+          <t xml:space="preserve"> lacking order or planning </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> wise, intelligent, perceptive </t>
+          <t xml:space="preserve"> random, chaotic </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> foolish, ignorant </t>
+          <t xml:space="preserve"> organized, systematic </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The sagacious leader earned everyone's respect.  </t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve"> Books were arranged in a haphazard way.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2748,27 +2614,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tenacious </t>
+          <t xml:space="preserve"> Haughty </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holding firmly or persistently </t>
+          <t xml:space="preserve"> arrogantly superior </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> determined, persistent, strong-willed </t>
+          <t xml:space="preserve"> arrogant, proud </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> weak, surrendering </t>
+          <t xml:space="preserve"> humble, modest </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She was tenacious in chasing her dreams.  </t>
+          <t xml:space="preserve"> His haughty behavior annoyed everyone.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2779,27 +2645,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ubiquitous </t>
+          <t xml:space="preserve"> Heinous </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Present everywhere at once </t>
+          <t xml:space="preserve"> extremely wicked or shocking </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> omnipresent, universal, widespread </t>
+          <t xml:space="preserve"> atrocious, evil </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rare, scarce </t>
+          <t xml:space="preserve"> minor, trivial </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mobile phones have become ubiquitous today.  </t>
+          <t xml:space="preserve"> The court punished him for the heinous crime.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2810,27 +2676,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Vacillate </t>
+          <t xml:space="preserve"> Idiosyncratic </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To waver between choices </t>
+          <t xml:space="preserve"> peculiar to an individual </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> hesitate, fluctuate, sway </t>
+          <t xml:space="preserve"> peculiar, distinctive </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> decide, persist </t>
+          <t xml:space="preserve"> common, ordinary </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He tends to vacillate on important decisions.  </t>
+          <t xml:space="preserve"> His idiosyncratic behavior made him unique.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -2841,27 +2707,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Wistful </t>
+          <t xml:space="preserve"> Illicit </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Longing or yearning with sadness </t>
+          <t xml:space="preserve"> illegal or forbidden </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> nostalgic, melancholy, reflective </t>
+          <t xml:space="preserve"> illegal, unlawful </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> content, joyful </t>
+          <t xml:space="preserve"> legal, lawful </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She looked wistful while staring at old photos.  </t>
+          <t xml:space="preserve"> The police cracked down on illicit trade.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -2872,27 +2738,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Xenophobic </t>
+          <t xml:space="preserve"> Immaculate </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fearful or hateful of foreigners </t>
+          <t xml:space="preserve"> perfectly clean or pure </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> intolerant, biased, prejudiced </t>
+          <t xml:space="preserve"> spotless, flawless </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tolerant, accepting </t>
+          <t xml:space="preserve"> dirty, flawed </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The policy was criticized as xenophobic.  </t>
+          <t xml:space="preserve"> The room was immaculate after cleaning.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -2903,27 +2769,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Yoke </t>
+          <t xml:space="preserve"> Imminent </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To join together or burden </t>
+          <t xml:space="preserve"> about to happen </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> bind, connect, harness </t>
+          <t xml:space="preserve"> impending, approaching </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> release, free </t>
+          <t xml:space="preserve"> distant, remote </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> They were yoked by a common goal.  </t>
+          <t xml:space="preserve"> A storm is imminent according to the forecast.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -2934,27 +2800,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abnegation </t>
+          <t xml:space="preserve"> Immutable </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The act of renouncing or rejecting something </t>
+          <t xml:space="preserve"> unchanging over time </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> denial, refusal, renunciation </t>
+          <t xml:space="preserve"> fixed, unchangeable </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> acceptance, approval </t>
+          <t xml:space="preserve"> alterable, flexible </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His abnegation of worldly pleasures was admirable.  </t>
+          <t xml:space="preserve"> Moral principles should be immutable.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -2965,27 +2831,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Bellwether </t>
+          <t xml:space="preserve"> Impartial </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An indicator or leader of a trend </t>
+          <t xml:space="preserve"> not taking sides </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> leader, forerunner, pioneer </t>
+          <t xml:space="preserve"> neutral, unbiased </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> follower, laggard </t>
+          <t xml:space="preserve"> biased, partial </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The company is a bellwether in the tech industry.  </t>
+          <t xml:space="preserve"> Judges must remain impartial in court.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -2996,27 +2862,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circumspect </t>
+          <t xml:space="preserve"> Impeccable </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cautious and unwilling to take risks </t>
+          <t xml:space="preserve"> perfect and without mistakes </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> careful, wary, prudent </t>
+          <t xml:space="preserve"> flawless, perfect </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> reckless, careless </t>
+          <t xml:space="preserve"> faulty, imperfect </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She was circumspect in making financial decisions.  </t>
+          <t xml:space="preserve"> Her pronunciation was impeccable.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -3027,27 +2893,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Defenestrate </t>
+          <t xml:space="preserve"> Impetuous </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To throw someone out of a window </t>
+          <t xml:space="preserve"> acting without thinking </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> eject, expel, toss </t>
+          <t xml:space="preserve"> rash, hasty </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> retain, keep </t>
+          <t xml:space="preserve"> cautious, careful </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The protesters threatened to defenestrate the corrupt official.  </t>
+          <t xml:space="preserve"> His impetuous decision caused problems.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -3058,27 +2924,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Excoriate </t>
+          <t xml:space="preserve"> Implicit </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To criticize severely </t>
+          <t xml:space="preserve"> implied but not directly stated </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> censure, condemn, denounce </t>
+          <t xml:space="preserve"> implied, indirect </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> praise, commend </t>
+          <t xml:space="preserve"> explicit, direct </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The critic excoriated the new play in her review.  </t>
+          <t xml:space="preserve"> There was implicit criticism in his remark.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -3089,27 +2955,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fatuous </t>
+          <t xml:space="preserve"> Incentive </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Silly and pointless </t>
+          <t xml:space="preserve"> something that motivates </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> foolish, inane, stupid </t>
+          <t xml:space="preserve"> motivation, stimulus </t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> sensible, intelligent </t>
+          <t xml:space="preserve"> deterrent, disincentive </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His fatuous remarks annoyed everyone.  </t>
+          <t xml:space="preserve"> Bonuses act as incentives for employees.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3120,27 +2986,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grandiloquent </t>
+          <t xml:space="preserve"> Incessant </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pompous or extravagant in language </t>
+          <t xml:space="preserve"> continuing without stopping </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> pretentious, bombastic, flowery </t>
+          <t xml:space="preserve"> constant, nonstop </t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> simple, plain </t>
+          <t xml:space="preserve"> occasional, intermittent </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The politician's grandiloquent speech failed to impress.  </t>
+          <t xml:space="preserve"> The incessant rain caused flooding.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -3151,27 +3017,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hegemony </t>
+          <t xml:space="preserve"> Incisive </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leadership or dominance, especially by one country </t>
+          <t xml:space="preserve"> clear and direct expression </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dominance, control, authority </t>
+          <t xml:space="preserve"> sharp, penetrating </t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> subordination, submission </t>
+          <t xml:space="preserve"> vague, dull </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The empire maintained hegemony over the region.  </t>
+          <t xml:space="preserve"> Her incisive analysis impressed the professor.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3182,27 +3048,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inimical </t>
+          <t xml:space="preserve"> Indignant </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hostile or harmful </t>
+          <t xml:space="preserve"> angry at unfair treatment </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> antagonistic, adverse, unfriendly </t>
+          <t xml:space="preserve"> angry, resentful </t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> favorable, beneficial </t>
+          <t xml:space="preserve"> pleased, content </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Policies inimical to economic growth were rejected.  </t>
+          <t xml:space="preserve"> She became indignant at the unfair accusation.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3213,27 +3079,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jejune </t>
+          <t xml:space="preserve"> Indolent </t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Naive, simplistic, and superficial </t>
+          <t xml:space="preserve"> lazy and avoiding activity </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> immature, simplistic, dull </t>
+          <t xml:space="preserve"> lazy, idle </t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> mature, sophisticated </t>
+          <t xml:space="preserve"> hardworking, active </t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The book's plot was jejune and predictable.  </t>
+          <t xml:space="preserve"> He became indolent after getting the job.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -3244,27 +3110,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lachrymose </t>
+          <t xml:space="preserve"> Inept </t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tearful or given to weeping </t>
+          <t xml:space="preserve"> showing no skill </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tearful, mournful, sorrowful </t>
+          <t xml:space="preserve"> incompetent, clumsy </t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> joyful, happy </t>
+          <t xml:space="preserve"> skilled, competent </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The lachrymose movie made many cry.  </t>
+          <t xml:space="preserve"> His inept handling of the situation caused chaos.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3275,27 +3141,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mendacious </t>
+          <t xml:space="preserve"> Inhibit </t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not telling the truth; lying </t>
+          <t xml:space="preserve"> prevent or restrain </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> untruthful, deceitful, dishonest </t>
+          <t xml:space="preserve"> hinder, restrict </t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> truthful, honest </t>
+          <t xml:space="preserve"> encourage, allow </t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His mendacious statements damaged his reputation.  </t>
+          <t xml:space="preserve"> Fear can inhibit people from speaking English.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -3306,27 +3172,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nefarious </t>
+          <t xml:space="preserve"> Innate </t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Wicked or criminal </t>
+          <t xml:space="preserve"> existing from birth </t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> evil, villainous, heinous </t>
+          <t xml:space="preserve"> natural, inborn </t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> virtuous, honorable </t>
+          <t xml:space="preserve"> acquired, learned </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The villain's nefarious plot was foiled.  </t>
+          <t xml:space="preserve"> She has innate musical talent.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -3337,27 +3203,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obsequious </t>
+          <t xml:space="preserve"> Insatiable </t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Excessively eager to please or obey </t>
+          <t xml:space="preserve"> impossible to satisfy </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> servile, sycophantic, fawning </t>
+          <t xml:space="preserve"> greedy, voracious </t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> assertive, domineering </t>
+          <t xml:space="preserve"> satisfied, content </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The obsequious assistant annoyed his boss.  </t>
+          <t xml:space="preserve"> His insatiable curiosity led him to study science.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -3368,27 +3234,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Paragon </t>
+          <t xml:space="preserve"> Intransigent </t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A model of excellence or perfection </t>
+          <t xml:space="preserve"> unwilling to change views </t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> exemplar, ideal, archetype </t>
+          <t xml:space="preserve"> stubborn, inflexible </t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> flaw, imperfection </t>
+          <t xml:space="preserve"> flexible, yielding </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She was a paragon of virtue in the community.  </t>
+          <t xml:space="preserve"> The parties remained intransigent during talks.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3399,27 +3265,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quagmire </t>
+          <t xml:space="preserve"> Intrepid </t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A difficult or precarious situation </t>
+          <t xml:space="preserve"> fearless and adventurous </t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> predicament, dilemma, morass </t>
+          <t xml:space="preserve"> brave, courageous </t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> solution, relief </t>
+          <t xml:space="preserve"> fearful, timid </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The country found itself in a political quagmire.  </t>
+          <t xml:space="preserve"> Intrepid climbers reached the summit.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -3430,27 +3296,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reprobate </t>
+          <t xml:space="preserve"> Irascible </t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An unprincipled or wicked person </t>
+          <t xml:space="preserve"> easily angered </t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> scoundrel, rogue, villain </t>
+          <t xml:space="preserve"> irritable, hot-tempered </t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> saint, hero </t>
+          <t xml:space="preserve"> calm, patient </t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The reprobate was known for his crimes.  </t>
+          <t xml:space="preserve"> His irascible nature made teamwork difficult.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -3461,27 +3327,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sycophant </t>
+          <t xml:space="preserve"> Judicious </t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Someone who flatters for personal gain </t>
+          <t xml:space="preserve"> showing good judgment </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> flatterer, toady, bootlicker </t>
+          <t xml:space="preserve"> wise, sensible </t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> critic, challenger </t>
+          <t xml:space="preserve"> foolish, reckless </t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The manager surrounded himself with sycophants.  </t>
+          <t xml:space="preserve"> Make judicious use of your study time.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -3492,27 +3358,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tautological </t>
+          <t xml:space="preserve"> Lament </t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Needless repetition; redundant </t>
+          <t xml:space="preserve"> express sorrow </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> repetitive, redundant, circular </t>
+          <t xml:space="preserve"> mourn, grieve </t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> concise, brief </t>
+          <t xml:space="preserve"> celebrate, rejoice </t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His explanation was tautological and boring.  </t>
+          <t xml:space="preserve"> People lamented the leader’s death.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -3523,27 +3389,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Uxorious </t>
+          <t xml:space="preserve"> Lavish </t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Excessively devoted to one's wife </t>
+          <t xml:space="preserve"> rich, elaborate or luxurious </t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> doting, submissive, loving </t>
+          <t xml:space="preserve"> extravagant, opulent </t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> indifferent, neglectful </t>
+          <t xml:space="preserve"> simple, frugal </t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The uxorious husband bought his wife many gifts.  </t>
+          <t xml:space="preserve"> The wedding was lavish and expensive.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -3554,27 +3420,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Vicissitude </t>
+          <t xml:space="preserve"> Lethargic </t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A change or variation occurring in the course of something </t>
+          <t xml:space="preserve"> lacking energy </t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fluctuation, change, shift </t>
+          <t xml:space="preserve"> sluggish, tired </t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> stability, permanence </t>
+          <t xml:space="preserve"> energetic, lively </t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The vicissitudes of life can be challenging.  </t>
+          <t xml:space="preserve"> He felt lethargic after the long flight.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -3585,27 +3451,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Winsome </t>
+          <t xml:space="preserve"> Lucid </t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Attractive or charming in a sweet way </t>
+          <t xml:space="preserve"> expressed clearly </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> charming, appealing, engaging </t>
+          <t xml:space="preserve"> clear, coherent </t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> unattractive, repellent </t>
+          <t xml:space="preserve"> confused, unclear </t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Her winsome smile won everyone's heart.  </t>
+          <t xml:space="preserve"> Her explanation was lucid and easy to follow.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -3616,27 +3482,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Xenial </t>
+          <t xml:space="preserve"> Magnitude </t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hospitable, especially to strangers or guests </t>
+          <t xml:space="preserve"> great size or importance </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> hospitable, welcoming, friendly </t>
+          <t xml:space="preserve"> extent, scale </t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> inhospitable, unfriendly </t>
+          <t xml:space="preserve"> insignificance, triviality </t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The hosts were very xenial to their guests.  </t>
+          <t xml:space="preserve"> The magnitude of the problem surprised them.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -3647,27 +3513,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Yare </t>
+          <t xml:space="preserve"> Malevolent </t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ready, prepared, or agile </t>
+          <t xml:space="preserve"> wishing evil on others </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ready, prepared, nimble </t>
+          <t xml:space="preserve"> malicious, spiteful </t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> clumsy, slow </t>
+          <t xml:space="preserve"> benevolent, kind </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The sailors were yare and efficient in their duties.  </t>
+          <t xml:space="preserve"> The villain had a malevolent smile.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -3678,27 +3544,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zephyr </t>
+          <t xml:space="preserve"> Malign </t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A gentle, mild breeze </t>
+          <t xml:space="preserve"> speak harmful untruths about </t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> breeze, wind, gust </t>
+          <t xml:space="preserve"> slander, defame </t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> gale, storm </t>
+          <t xml:space="preserve"> praise, commend </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The zephyr cooled the hot summer afternoon.  </t>
+          <t xml:space="preserve"> He was maligned by false rumors.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -3709,27 +3575,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abscond </t>
+          <t xml:space="preserve"> Malleable </t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To leave hurriedly and secretly </t>
+          <t xml:space="preserve"> easily influenced or shaped </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> flee, escape, bolt </t>
+          <t xml:space="preserve"> flexible, adaptable </t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> remain, stay </t>
+          <t xml:space="preserve"> rigid, inflexible </t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The thief absconded with the stolen jewels.  </t>
+          <t xml:space="preserve"> Children’s minds are highly malleable.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -3740,27 +3606,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Bilk </t>
+          <t xml:space="preserve"> Meander </t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To cheat or defraud </t>
+          <t xml:space="preserve"> wander without direction </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> swindle, cheat, deceive </t>
+          <t xml:space="preserve"> roam, drift </t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> give, reward </t>
+          <t xml:space="preserve"> hurry, rush </t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The con artist bilked investors out of millions.  </t>
+          <t xml:space="preserve"> We meandered through the old streets.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -3771,27 +3637,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Concatenation </t>
+          <t xml:space="preserve"> Meticulous </t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A series of interconnected things or events </t>
+          <t xml:space="preserve"> extremely careful with details </t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> sequence, chain, link </t>
+          <t xml:space="preserve"> careful, precise </t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> separation, disconnection </t>
+          <t xml:space="preserve"> careless, sloppy </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The novel had a concatenation of plot twists.  </t>
+          <t xml:space="preserve"> She is meticulous when checking essays.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -3802,27 +3668,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Demagogue </t>
+          <t xml:space="preserve"> Mitigate </t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A political leader who seeks support by appealing to desires and prejudices </t>
+          <t xml:space="preserve"> make less severe </t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> agitator, rabble-rouser, fanatic </t>
+          <t xml:space="preserve"> reduce, ease </t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> peacemaker, moderate </t>
+          <t xml:space="preserve"> worsen, aggravate </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The demagogue stirred unrest among the people.  </t>
+          <t xml:space="preserve"> Measures were taken to mitigate pollution.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -3833,27 +3699,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Enervate </t>
+          <t xml:space="preserve"> Mundane </t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To weaken or drain energy </t>
+          <t xml:space="preserve"> ordinary and dull </t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> exhaust, debilitate, tire </t>
+          <t xml:space="preserve"> routine, boring </t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> energize, strengthen </t>
+          <t xml:space="preserve"> exciting, extraordinary </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The hot sun enervated the marathon runners.  </t>
+          <t xml:space="preserve"> He was tired of his mundane office job.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -3864,27 +3730,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fecund </t>
+          <t xml:space="preserve"> Nebulous </t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fertile or productive </t>
+          <t xml:space="preserve"> unclear or vague </t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fruitful, prolific, fertile </t>
+          <t xml:space="preserve"> vague, hazy </t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> barren, infertile </t>
+          <t xml:space="preserve"> clear, definite </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The fecund soil yielded a rich harvest.  </t>
+          <t xml:space="preserve"> His idea remained nebulous and unformed.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -3895,27 +3761,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grandiose </t>
+          <t xml:space="preserve"> Nefarious </t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impressive but unrealistic or overblown </t>
+          <t xml:space="preserve"> extremely wicked </t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> magnificent, extravagant, pompous </t>
+          <t xml:space="preserve"> evil, villainous </t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> modest, simple </t>
+          <t xml:space="preserve"> noble, good </t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The grandiose plan failed due to lack of funds.  </t>
+          <t xml:space="preserve"> The gang carried out nefarious activities.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -3926,27 +3792,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Histrionic </t>
+          <t xml:space="preserve"> Nemesis </t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Overly theatrical or dramatic </t>
+          <t xml:space="preserve"> agent of downfall </t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> theatrical, exaggerated, melodramatic </t>
+          <t xml:space="preserve"> rival, opponent </t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> restrained, subdued </t>
+          <t xml:space="preserve"> supporter, friend </t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Her histrionic behavior annoyed her coworkers.  </t>
+          <t xml:space="preserve"> His laziness became his nemesis.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -3957,27 +3823,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inchoate </t>
+          <t xml:space="preserve"> Nonchalant </t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Just begun and not fully formed </t>
+          <t xml:space="preserve"> calm and unconcerned </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rudimentary, undeveloped, embryonic </t>
+          <t xml:space="preserve"> indifferent, relaxed </t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> developed, mature </t>
+          <t xml:space="preserve"> anxious, concerned </t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The project is still in an inchoate stage.  </t>
+          <t xml:space="preserve"> He seemed nonchalant about the exam.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -3988,27 +3854,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Juxtaposition </t>
+          <t xml:space="preserve"> Notorious </t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The act of placing things side by side for comparison </t>
+          <t xml:space="preserve"> famous for something bad </t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> adjacency, proximity, contrast </t>
+          <t xml:space="preserve"> infamous, disreputable </t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> separation, distance </t>
+          <t xml:space="preserve"> reputable, respected </t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The artist's work showed a juxtaposition of old and new styles.  </t>
+          <t xml:space="preserve"> The street is notorious for crime.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -4019,27 +3885,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lachrymose </t>
+          <t xml:space="preserve"> Novel </t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tearfully or excessively sentimental </t>
+          <t xml:space="preserve"> new or unusual </t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tearful, weepy, mournful </t>
+          <t xml:space="preserve"> innovative, original </t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> cheerful, joyful </t>
+          <t xml:space="preserve"> common, ordinary </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The lachrymose novel moved many readers to tears.  </t>
+          <t xml:space="preserve"> He proposed a novel solution.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -4050,27 +3916,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mendicant </t>
+          <t xml:space="preserve"> Nuance </t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beggar; someone who lives by asking for charity </t>
+          <t xml:space="preserve"> subtle difference </t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> beggar, pauper, panhandler </t>
+          <t xml:space="preserve"> shade, distinction </t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> wealthy, rich </t>
+          <t xml:space="preserve"> bluntness, clarity </t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The mendicant sat at the corner hoping for alms.  </t>
+          <t xml:space="preserve"> Understanding nuance improves language skills.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -4081,27 +3947,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Noisome </t>
+          <t xml:space="preserve"> Oblivious </t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Offensive or disgusting, especially to the sense of smell </t>
+          <t xml:space="preserve"> unaware of what is happening </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> foul, unpleasant, noxious </t>
+          <t xml:space="preserve"> unaware, ignorant </t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> pleasant, fragrant </t>
+          <t xml:space="preserve"> aware, conscious </t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The noisome garbage caused a terrible smell.  </t>
+          <t xml:space="preserve"> She walked on oblivious to the traffic.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -4112,27 +3978,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obstreperous </t>
+          <t xml:space="preserve"> Obscure </t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Noisy and difficult to control </t>
+          <t xml:space="preserve"> not well known </t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> unruly, boisterous, rowdy </t>
+          <t xml:space="preserve"> unknown, hidden </t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> quiet, obedient </t>
+          <t xml:space="preserve"> famous, clear </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The obstreperous crowd disrupted the meeting.  </t>
+          <t xml:space="preserve"> The author remained obscure for years.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -4143,27 +4009,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Perspicacious </t>
+          <t xml:space="preserve"> Obstinate </t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Having keen insight or understanding </t>
+          <t xml:space="preserve"> stubbornly refusing to change </t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> perceptive, insightful, astute </t>
+          <t xml:space="preserve"> stubborn, inflexible </t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dull, ignorant </t>
+          <t xml:space="preserve"> flexible, compliant </t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The perspicacious detective solved the case quickly.  </t>
+          <t xml:space="preserve"> He remained obstinate despite advice.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -4174,27 +4040,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quiescent </t>
+          <t xml:space="preserve"> Ominous </t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> In a state of inactivity or dormancy </t>
+          <t xml:space="preserve"> suggesting something bad </t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dormant, inactive, still </t>
+          <t xml:space="preserve"> threatening, menacing </t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> active, lively </t>
+          <t xml:space="preserve"> promising, hopeful </t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The volcano remained quiescent for decades.  </t>
+          <t xml:space="preserve"> Dark clouds created an ominous mood.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -4205,27 +4071,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Recalcitrant </t>
+          <t xml:space="preserve"> Onerous </t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stubbornly resistant to authority </t>
+          <t xml:space="preserve"> involving great effort </t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> defiant, disobedient, uncooperative </t>
+          <t xml:space="preserve"> burdensome, heavy </t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> compliant, obedient </t>
+          <t xml:space="preserve"> easy, light </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The recalcitrant employee refused to follow instructions.  </t>
+          <t xml:space="preserve"> The task became onerous over time.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -4236,27 +4102,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Salubrious </t>
+          <t xml:space="preserve"> Opaque </t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Health-giving; healthy </t>
+          <t xml:space="preserve"> not transparent or clear </t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> beneficial, wholesome, healthful </t>
+          <t xml:space="preserve"> cloudy, unclear </t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> harmful, unhealthy </t>
+          <t xml:space="preserve"> clear, transparent </t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The mountain air was salubrious and invigorating.  </t>
+          <t xml:space="preserve"> The explanation was opaque and confusing.</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -4267,27 +4133,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tautological </t>
+          <t xml:space="preserve"> Ostentatious </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Redundant or needlessly repetitive </t>
+          <t xml:space="preserve"> showy and designed to impress </t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> repetitive, redundant, circular </t>
+          <t xml:space="preserve"> showy, flashy </t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> concise, succinct </t>
+          <t xml:space="preserve"> modest, simple </t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His argument was tautological and boring.  </t>
+          <t xml:space="preserve"> He wore ostentatious gold jewelry.</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -4298,27 +4164,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Umbrageous </t>
+          <t xml:space="preserve"> Overt </t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Shady or shadowy; inclined to take offense easily </t>
+          <t xml:space="preserve"> done openly </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> shady, sensitive, touchy </t>
+          <t xml:space="preserve"> open, obvious </t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> unoffended, insensitive </t>
+          <t xml:space="preserve"> hidden, secret </t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The umbrageous path offered relief from the sun.  </t>
+          <t xml:space="preserve"> There was overt disagreement in the meeting.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -4329,27 +4195,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Verbose </t>
+          <t xml:space="preserve"> Palpable </t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Using more words than needed </t>
+          <t xml:space="preserve"> able to be felt or touched </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> wordy, long-winded, talkative </t>
+          <t xml:space="preserve"> tangible, obvious </t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> concise, brief </t>
+          <t xml:space="preserve"> hidden, unseen </t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The professor’s verbose lecture lost the students’ attention.  </t>
+          <t xml:space="preserve"> The tension in the room was palpable.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -4360,27 +4226,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Winsome </t>
+          <t xml:space="preserve"> Paradox </t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Charming and pleasing </t>
+          <t xml:space="preserve"> self-contradictory statement </t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> charming, attractive, engaging </t>
+          <t xml:space="preserve"> contradiction, puzzle </t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> repulsive, unattractive </t>
+          <t xml:space="preserve"> clarity, certainty </t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Her winsome smile captivated everyone.  </t>
+          <t xml:space="preserve"> The statement “less is more” is a paradox.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -4391,27 +4257,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Xeric </t>
+          <t xml:space="preserve"> Paramount </t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Characterized by very dry conditions </t>
+          <t xml:space="preserve"> more important than anything else </t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arid, dry, desert-like </t>
+          <t xml:space="preserve"> supreme, primary </t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> moist, humid </t>
+          <t xml:space="preserve"> minor, secondary </t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Xeric plants thrive in desert environments.  </t>
+          <t xml:space="preserve"> Education is of paramount importance.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -4422,27 +4288,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Yawp </t>
+          <t xml:space="preserve"> Parsimonious </t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To shout or cry loudly </t>
+          <t xml:space="preserve"> unwilling to spend money </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> yell, shout, scream </t>
+          <t xml:space="preserve"> stingy, miserly </t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> whisper, murmur </t>
+          <t xml:space="preserve"> generous, liberal </t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The crowd began to yawp after the game ended.  </t>
+          <t xml:space="preserve"> He is too parsimonious to donate.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -4453,27 +4319,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zealous </t>
+          <t xml:space="preserve"> Partisan </t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Filled with or motivated by enthusiasm </t>
+          <t xml:space="preserve"> strongly supporting one side </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fervent, passionate, ardent </t>
+          <t xml:space="preserve"> biased, one-sided </t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> indifferent, apathetic </t>
+          <t xml:space="preserve"> neutral, impartial </t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The zealous volunteers worked tirelessly.  </t>
+          <t xml:space="preserve"> The media became partisan in reporting.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -4484,27 +4350,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abrogate </t>
+          <t xml:space="preserve"> Paucity </t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To repeal or do away with a law or agreement </t>
+          <t xml:space="preserve"> presence of something in small amount </t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> annul, revoke, cancel </t>
+          <t xml:space="preserve"> scarcity, shortage </t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> enact, establish </t>
+          <t xml:space="preserve"> abundance, plenty </t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The government decided to abrogate the outdated law.  </t>
+          <t xml:space="preserve"> There is a paucity of clean water.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -4515,27 +4381,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Bilious </t>
+          <t xml:space="preserve"> Pecuniary </t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Bad-tempered or spiteful </t>
+          <t xml:space="preserve"> relating to money </t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> irritable, grumpy, choleric </t>
+          <t xml:space="preserve"> financial, monetary </t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> cheerful, pleasant </t>
+          <t xml:space="preserve"> nonfinancial, nonmaterial </t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His bilious remarks upset everyone at the meeting.  </t>
+          <t xml:space="preserve"> He faced pecuniary difficulties after losing his job.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -4546,27 +4412,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Conflagration </t>
+          <t xml:space="preserve"> Perceptive </t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A large destructive fire </t>
+          <t xml:space="preserve"> showing sensitive insight </t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> blaze, inferno, wildfire </t>
+          <t xml:space="preserve"> observant, insightful </t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> drizzle, shower </t>
+          <t xml:space="preserve"> oblivious, unaware </t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The conflagration destroyed several buildings downtown.  </t>
+          <t xml:space="preserve"> She is perceptive and notices small details.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -4577,27 +4443,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Desultory </t>
+          <t xml:space="preserve"> Perennial </t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lacking a plan or purpose; random </t>
+          <t xml:space="preserve"> lasting a long time </t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> aimless, haphazard, erratic </t>
+          <t xml:space="preserve"> enduring, continual </t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> purposeful, deliberate </t>
+          <t xml:space="preserve"> temporary, short-lived </t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His desultory speech failed to impress the audience.  </t>
+          <t xml:space="preserve"> Poverty is a perennial issue in many countries.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -4608,27 +4474,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Effulgent </t>
+          <t xml:space="preserve"> Pernicious </t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Shining brightly; radiant </t>
+          <t xml:space="preserve"> extremely harmful </t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> radiant, brilliant, dazzling </t>
+          <t xml:space="preserve"> damaging, destructive </t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dim, dull </t>
+          <t xml:space="preserve"> harmless, beneficial </t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The effulgent sun lit up the entire valley.  </t>
+          <t xml:space="preserve"> Pernicious rumors spread quickly online.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -4639,27 +4505,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fervid </t>
+          <t xml:space="preserve"> Persuasive </t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intensely passionate or enthusiastic </t>
+          <t xml:space="preserve"> able to convince </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ardent, fervent, zealous </t>
+          <t xml:space="preserve"> convincing, compelling </t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> indifferent, apathetic </t>
+          <t xml:space="preserve"> weak, ineffective </t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The crowd gave a fervid applause after the performance.  </t>
+          <t xml:space="preserve"> Her persuasive speech changed many minds.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -4670,27 +4536,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Garrulous </t>
+          <t xml:space="preserve"> Pessimistic </t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Excessively talkative, especially on trivial matters </t>
+          <t xml:space="preserve"> expecting bad outcomes </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> chatty, loquacious, verbose </t>
+          <t xml:space="preserve"> negative, gloomy </t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> taciturn, reserved </t>
+          <t xml:space="preserve"> optimistic, hopeful </t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The garrulous host dominated the conversation.  </t>
+          <t xml:space="preserve"> He is pessimistic about the economy.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -4701,27 +4567,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hegemony </t>
+          <t xml:space="preserve"> Placid </t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leadership or dominance, especially by one group over others </t>
+          <t xml:space="preserve"> calm and peaceful </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dominance, control, authority </t>
+          <t xml:space="preserve"> calm, tranquil </t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> subordination, submission </t>
+          <t xml:space="preserve"> agitated, disturbed </t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The country maintained its hegemony over the region for decades.  </t>
+          <t xml:space="preserve"> The lake looked placid in the evening.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -4732,27 +4598,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Insouciant </t>
+          <t xml:space="preserve"> Plausible </t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Showing a casual lack of concern; indifferent </t>
+          <t xml:space="preserve"> seeming reasonable </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> nonchalant, unconcerned, carefree </t>
+          <t xml:space="preserve"> believable, credible </t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> worried, anxious </t>
+          <t xml:space="preserve"> improbable, unlikely </t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She gave an insouciant shrug despite the looming deadline.  </t>
+          <t xml:space="preserve"> His excuse sounded plausible.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -4763,27 +4629,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jejune </t>
+          <t xml:space="preserve"> Pragmatic </t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Naive, simplistic, and superficial </t>
+          <t xml:space="preserve"> realistic and practical </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> immature, simplistic, dull </t>
+          <t xml:space="preserve"> practical, realistic </t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> mature, sophisticated </t>
+          <t xml:space="preserve"> idealistic, impractical </t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The novel’s plot was jejune and unengaging.  </t>
+          <t xml:space="preserve"> She took a pragmatic approach to the issue.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -4794,27 +4660,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Kowtow </t>
+          <t xml:space="preserve"> Precarious </t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To act in a subservient manner </t>
+          <t xml:space="preserve"> not securely held </t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> grovel, bow, fawn </t>
+          <t xml:space="preserve"> unstable, risky </t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> resist, defy </t>
+          <t xml:space="preserve"> safe, secure </t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He refused to kowtow to the corrupt officials.  </t>
+          <t xml:space="preserve"> The ladder looked precarious.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -4825,27 +4691,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lachrymose </t>
+          <t xml:space="preserve"> Preclude </t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tearfully or excessively sentimental </t>
+          <t xml:space="preserve"> prevent from happening </t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tearful, weepy, mournful </t>
+          <t xml:space="preserve"> prevent, hinder </t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> cheerful, joyful </t>
+          <t xml:space="preserve"> allow, permit </t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The lachrymose film brought tears to many viewers.  </t>
+          <t xml:space="preserve"> His injury precluded participation in the match.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -4856,27 +4722,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mendacious </t>
+          <t xml:space="preserve"> Predicament </t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lying; untruthful </t>
+          <t xml:space="preserve"> difficult situation </t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> deceitful, dishonest, untruthful </t>
+          <t xml:space="preserve"> dilemma, difficulty </t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> honest, truthful </t>
+          <t xml:space="preserve"> solution, advantage </t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His mendacious stories damaged his credibility.  </t>
+          <t xml:space="preserve"> He found himself in an embarrassing predicament.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -4887,27 +4753,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nefarious </t>
+          <t xml:space="preserve"> Procrastinate </t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Wicked or criminal </t>
+          <t xml:space="preserve"> delay doing something </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> villainous, evil, heinous </t>
+          <t xml:space="preserve"> delay, postpone </t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> virtuous, righteous </t>
+          <t xml:space="preserve"> hasten, advance </t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The nefarious scheme was uncovered by the police.  </t>
+          <t xml:space="preserve"> Students often procrastinate before exams.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -4918,27 +4784,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obstreperous </t>
+          <t xml:space="preserve"> Prolific </t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Noisy and difficult to control </t>
+          <t xml:space="preserve"> producing many works </t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> unruly, boisterous, rowdy </t>
+          <t xml:space="preserve"> productive, fertile </t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> quiet, obedient </t>
+          <t xml:space="preserve"> unproductive, barren </t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The obstreperous crowd was difficult to manage.  </t>
+          <t xml:space="preserve"> She is a prolific writer.</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -4949,27 +4815,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pernicious </t>
+          <t xml:space="preserve"> Prudent </t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Having a harmful effect, especially in a gradual way </t>
+          <t xml:space="preserve"> acting with care and thought </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> harmful, damaging, deleterious </t>
+          <t xml:space="preserve"> wise, cautious </t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> beneficial, harmless </t>
+          <t xml:space="preserve"> reckless, careless </t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The pernicious influence of social media is a concern.  </t>
+          <t xml:space="preserve"> It is prudent to save money for emergencies.</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -4980,27 +4846,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Quixotic </t>
+          <t xml:space="preserve"> Quandary </t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unrealistic and impractical </t>
+          <t xml:space="preserve"> state of uncertainty </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> idealistic, romantic, impractical </t>
+          <t xml:space="preserve"> dilemma, confusion </t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> pragmatic, realistic </t>
+          <t xml:space="preserve"> certainty, clarity </t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His quixotic dreams of fame never materialized.  </t>
+          <t xml:space="preserve"> He was in a quandary about the decision.</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -5011,27 +4877,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Recalcitrant </t>
+          <t xml:space="preserve"> Querulous </t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Resistant to authority or control </t>
+          <t xml:space="preserve"> complaining in a whining manner </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> defiant, disobedient, uncooperative </t>
+          <t xml:space="preserve"> complaining, grumbling </t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> compliant, obedient </t>
+          <t xml:space="preserve"> cheerful, content </t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The recalcitrant student refused to follow the rules.  </t>
+          <t xml:space="preserve"> The child became querulous during the trip.</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -5042,27 +4908,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sagacious </t>
+          <t xml:space="preserve"> Quiescent </t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Wise and keen in judgment </t>
+          <t xml:space="preserve"> in a state of inactivity </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> wise, insightful, shrewd </t>
+          <t xml:space="preserve"> inactive, dormant </t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> foolish, ignorant </t>
+          <t xml:space="preserve"> active, lively </t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The sagacious judge made a fair decision.  </t>
+          <t xml:space="preserve"> The volcano is currently quiescent.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -5073,27 +4939,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tenebrous </t>
+          <t xml:space="preserve"> Rambunctious </t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dark, shadowy, or obscure </t>
+          <t xml:space="preserve"> uncontrollably exuberant </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> gloomy, murky, dim </t>
+          <t xml:space="preserve"> boisterous, noisy </t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> bright, luminous </t>
+          <t xml:space="preserve"> quiet, calm </t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The tenebrous alley was avoided by locals after dusk.  </t>
+          <t xml:space="preserve"> Rambunctious children filled the playground.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -5104,27 +4970,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ubiquitous </t>
+          <t xml:space="preserve"> Rancor </t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Present everywhere </t>
+          <t xml:space="preserve"> long-lasting bitterness </t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> omnipresent, pervasive, universal </t>
+          <t xml:space="preserve"> bitterness, resentment </t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rare, scarce </t>
+          <t xml:space="preserve"> goodwill, kindness </t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smartphones are ubiquitous in modern society.  </t>
+          <t xml:space="preserve"> There was no rancor after their disagreement.</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -5135,27 +5001,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Vacillate </t>
+          <t xml:space="preserve"> Ravenous </t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To waver between different opinions or actions </t>
+          <t xml:space="preserve"> extremely hungry </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> hesitate, fluctuate, oscillate </t>
+          <t xml:space="preserve"> starving, famished </t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> decide, settle </t>
+          <t xml:space="preserve"> full, satisfied </t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> He tends to vacillate when faced with difficult choices.  </t>
+          <t xml:space="preserve"> After fasting, he felt ravenous.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -5166,27 +5032,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Wistful </t>
+          <t xml:space="preserve"> Rebut </t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Having a feeling of vague or regretful longing </t>
+          <t xml:space="preserve"> prove something false </t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> nostalgic, melancholic, reflective </t>
+          <t xml:space="preserve"> refute, disprove </t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> content, happy </t>
+          <t xml:space="preserve"> prove, confirm </t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> She felt wistful remembering her childhood home.  </t>
+          <t xml:space="preserve"> She rebutted the accusations with evidence.</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -5197,27 +5063,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Xenophobia </t>
+          <t xml:space="preserve"> Reclusive </t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dislike of or prejudice against foreigners </t>
+          <t xml:space="preserve"> avoiding company of others </t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> racism, intolerance, bigotry </t>
+          <t xml:space="preserve"> solitary, isolated </t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tolerance, acceptance </t>
+          <t xml:space="preserve"> sociable, outgoing </t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Xenophobia has increased tensions in the region.  </t>
+          <t xml:space="preserve"> The author lived a reclusive life.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -5228,30 +5094,1580 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Yoke </t>
+          <t xml:space="preserve"> Redundant </t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> To join together or to burden </t>
+          <t xml:space="preserve"> no longer needed </t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> bind, harness, couple </t>
+          <t xml:space="preserve"> unnecessary, surplus </t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> free, release </t>
+          <t xml:space="preserve"> essential, necessary </t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The farmer yoked the oxen to the plow.  </t>
+          <t xml:space="preserve"> Remove redundant words from essays.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Refute </t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> prove wrong </t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> disprove, contradict </t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> accept, admit </t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The scientist refuted the old theory.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Relinquish </t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> voluntarily give up </t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> surrender, abandon </t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> keep, retain </t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He relinquished control of the company.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Remorse </t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> deep regret for wrongdoing </t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> regret, guilt </t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> pride, satisfaction </t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He showed remorse for his mistakes.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Repercussion </t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> unintended consequence </t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> consequence, outcome </t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> cause, reason </t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The decision had economic repercussions.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Reproach </t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> express disapproval </t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> blame, criticize </t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> praise, commend </t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She looked at him with reproach.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rescind </t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> revoke or cancel </t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> cancel, withdraw </t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> enforce, establish </t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The offer was rescinded after review.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Resilient </t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> able to recover quickly </t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> tough, strong </t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> weak, fragile </t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Children are often resilient after setbacks.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Resolute </t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> admirably determined </t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> firm, determined </t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> hesitant, uncertain </t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She remained resolute in her goals.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rigorous </t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> extremely thorough </t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> strict, severe </t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> lenient, gentle </t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The selection process was rigorous.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rudimentary </t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> basic or simple </t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> basic, elementary </t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> advanced, complex </t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He has only rudimentary computer knowledge.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sagacious </t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> wise and shrewd </t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> wise, intelligent </t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> foolish, stupid </t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The sagacious leader made good decisions.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sanguine </t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> optimistic in a bad situation </t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> optimistic, hopeful </t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> pessimistic, gloomy </t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She remained sanguine about her future.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Scrutinize </t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> examine closely </t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> inspect, examine </t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ignore, neglect </t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The essay was scrutinized for plagiarism.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Serene </t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> calm and peaceful </t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> calm, tranquil </t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> noisy, chaotic </t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The morning sea looked serene.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Skeptical </t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> doubting or questioning </t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> doubtful, suspicious </t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> convinced, certain </t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Many people are skeptical of advertisements.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Solicit </t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ask for or try to obtain </t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> request, seek </t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> refuse, reject </t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The charity solicited donations.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Spontaneous </t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> unplanned or impulsive </t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> impulsive, instinctive </t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> planned, deliberate </t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Their trip was completely spontaneous.</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Spurious </t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> false but seeming true </t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> false, fake </t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> genuine, real </t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The article contained spurious claims.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Stagnant </t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> not moving or developing </t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> motionless, inactive </t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> active, flowing </t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The stagnant water attracted insects.</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Stringent </t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> very strict or severe </t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> strict, rigorous </t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> lenient, flexible </t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Airports have stringent security checks.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Substantiate </t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> provide evidence for </t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> prove, support </t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> disprove, contradict </t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Data were used to substantiate the theory.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Succinct </t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> briefly and clearly expressed </t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> concise, brief </t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> wordy, lengthy </t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Write answers in a succinct manner.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Superfluous </t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> unnecessary or excessive </t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> unnecessary, excess </t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> necessary, essential </t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Remove superfluous details from essays.</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Surreptitious </t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> kept secret because not approved </t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> secret, stealthy </t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> open, overt </t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> They held a surreptitious meeting.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tactful </t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> showing sensitivity in dealing with others </t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> diplomatic, polite </t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> rude, insensitive </t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She was tactful when correcting errors.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tenuous </t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> very weak or slight </t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> weak, fragile </t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> strong, firm </t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The evidence was tenuous and unconvincing.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Terse </t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> brief and unfriendly </t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> brief, curt </t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> polite, lengthy </t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> His answer was terse and annoyed her.</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Thwart </t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> prevent someone from doing something </t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> frustrate, hinder </t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> assist, help </t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The rain thwarted their plans.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Transient </t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> lasting only a short time </t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> temporary, brief </t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> permanent, lasting </t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Their happiness was transient.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Trepidation </t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> feeling of fear about something </t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> fear, anxiety </t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> confidence, calmness </t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She entered the room with trepidation.</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Trivial </t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> of little importance </t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> insignificant, minor </t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> important, significant </t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Do not focus on trivial mistakes.</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ubiquitous </t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> present everywhere </t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> widespread, universal </t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> rare, scarce </t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Smartphones are ubiquitous today.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Umbrage </t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> offense or annoyance </t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> offense, resentment </t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> satisfaction, pleasure </t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He took umbrage at the remark.</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Unprecedented </t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> never done before </t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> unparalleled, unheard-of </t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> common, ordinary </t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The pandemic created unprecedented challenges.</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Vacillate </t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> alternate between opinions </t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> hesitate, waver </t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> decide, determine </t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He vacillated between two job offers.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Vague </t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> not clearly expressed </t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> unclear, indistinct </t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> clear, specific </t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Her answer was vague and confusing.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Vehement </t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> showing strong feeling </t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> passionate, forceful </t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> mild, weak </t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She made a vehement protest.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Verbose </t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> using more words than needed </t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> wordy, long-winded </t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> concise, brief </t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Avoid verbose writing in IELTS essays.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Versatile </t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> able to do many things </t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> adaptable, flexible </t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> limited, restricted </t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He is a versatile musician.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Viable </t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> capable of working successfully </t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> workable, feasible </t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> impossible, impractical </t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> This is a viable business plan.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Vindicate </t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> clear from blame </t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> justify, exonerate </t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> blame, accuse </t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The evidence vindicated the suspect.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Virtuous </t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> behaving morally good </t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> moral, righteous </t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> immoral, wicked </t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She is known as a virtuous person.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Volatile </t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> likely to change suddenly </t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> unstable, explosive </t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> stable, calm </t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The political situation is volatile.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Voracious </t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> very eager for something </t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> greedy, insatiable </t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> satisfied, content </t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He is a voracious reader.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Wary </t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> cautious about dangers </t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> cautious, careful </t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> careless, reckless </t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Be wary of online scams.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Wholesome </t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> beneficial to health or morals </t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> healthy, beneficial </t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> harmful, unhealthy </t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> A wholesome diet is important.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Withstand </t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> resist or remain undamaged </t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> resist, endure </t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> surrender, yield </t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The building can withstand strong winds.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Wretched </t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> in a very unhappy state </t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> miserable, unhappy </t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> happy, joyful </t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The refugees were living in wretched conditions.</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Yearn </t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> long strongly for something </t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> long, desire </t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> dislike, reject </t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> She yearned to travel the world.</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Zealous </t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> showing great energy in pursuit of cause </t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> passionate, fervent </t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> indifferent, apathetic </t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> He is zealous about environmental protection.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -560,7 +560,9 @@
           <t xml:space="preserve"> Scientists studied the climate anomaly carefully.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -591,7 +593,9 @@
           <t xml:space="preserve"> The voters’ apathy affected the election turnout.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -622,7 +626,9 @@
           <t xml:space="preserve"> Preparing for IELTS can be an arduous task.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -653,7 +659,9 @@
           <t xml:space="preserve"> Her progress in English was astounding.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -684,7 +692,9 @@
           <t xml:space="preserve"> The room was austere but very clean.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -725,7 +725,9 @@
           <t xml:space="preserve"> His avarice led to unethical decisions.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -756,7 +758,9 @@
           <t xml:space="preserve"> His belligerent tone ended the conversation.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -787,7 +791,9 @@
           <t xml:space="preserve"> The doctor confirmed the tumor was benign.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -818,7 +824,9 @@
           <t xml:space="preserve"> Extra examples can bolster your argument.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -849,7 +857,9 @@
           <t xml:space="preserve"> She gave a candid opinion about the project.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -880,7 +890,9 @@
           <t xml:space="preserve"> The army had to capitulate after losing supplies.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -911,7 +923,9 @@
           <t xml:space="preserve"> His cogent explanation convinced the class.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -942,7 +956,9 @@
           <t xml:space="preserve"> A cohesive essay scores higher in IELTS writing.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -973,7 +989,9 @@
           <t xml:space="preserve"> He became complacent after small success.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1004,7 +1022,9 @@
           <t xml:space="preserve"> Quiet study rooms are conducive to learning.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1035,7 +1055,9 @@
           <t xml:space="preserve"> Choosing a career became a conundrum for her.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1066,7 +1088,9 @@
           <t xml:space="preserve"> The witness gave a credible statement.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1097,7 +1121,9 @@
           <t xml:space="preserve"> His cryptic message confused everyone.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1128,7 +1154,9 @@
           <t xml:space="preserve"> Many people are cynical about politics.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1159,7 +1187,9 @@
           <t xml:space="preserve"> Speaking in English can feel daunting at first.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1190,7 +1220,9 @@
           <t xml:space="preserve"> The disease can debilitate elderly patients.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1221,7 +1253,9 @@
           <t xml:space="preserve"> Students showed deference to their teacher.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1252,7 +1286,9 @@
           <t xml:space="preserve"> His insult was deliberate, not accidental.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -1319,7 +1319,9 @@
           <t xml:space="preserve"> The report delineates the new policy clearly.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -1352,7 +1352,9 @@
           <t xml:space="preserve"> The leader denounced corruption strongly.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1383,7 +1385,9 @@
           <t xml:space="preserve"> Many English words are derived from Latin.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1414,7 +1418,9 @@
           <t xml:space="preserve"> Smoking is detrimental to health.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1445,7 +1451,9 @@
           <t xml:space="preserve"> The book explains the dichotomy between rich and poor.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1476,7 +1484,9 @@
           <t xml:space="preserve"> The story had a didactic moral lesson.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -1517,7 +1517,9 @@
           <t xml:space="preserve"> Diligent students usually achieve higher bands.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1548,7 +1550,9 @@
           <t xml:space="preserve"> She was discreet when discussing personal matters.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1579,7 +1583,9 @@
           <t xml:space="preserve"> There was a discrepancy in the data.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1610,7 +1616,9 @@
           <t xml:space="preserve"> He spoke with disdain about cheating.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1641,7 +1649,9 @@
           <t xml:space="preserve"> He disparaged her ideas unfairly.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1672,7 +1682,9 @@
           <t xml:space="preserve"> Social media helps disseminate information.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1703,7 +1715,9 @@
           <t xml:space="preserve"> They had divergent opinions on the issue.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1734,7 +1748,9 @@
           <t xml:space="preserve"> The dog was surprisingly docile.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1765,7 +1781,9 @@
           <t xml:space="preserve"> He is dogmatic and never listens to others.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1796,7 +1814,9 @@
           <t xml:space="preserve"> His eccentric habits amused his friends.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1827,7 +1847,9 @@
           <t xml:space="preserve"> She has an eclectic taste in music.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1858,7 +1880,9 @@
           <t xml:space="preserve"> The company made an egregious mistake.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1889,7 +1913,9 @@
           <t xml:space="preserve"> She was elated after receiving the scholarship.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1920,7 +1946,9 @@
           <t xml:space="preserve"> The teacher elucidated the difficult topic.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1951,7 +1979,9 @@
           <t xml:space="preserve"> She gave an emphatic denial to the accusation.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1982,7 +2012,9 @@
           <t xml:space="preserve"> The conclusion is based on empirical data.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2013,7 +2045,9 @@
           <t xml:space="preserve"> Many celebrities endorse products.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2044,7 +2078,9 @@
           <t xml:space="preserve"> His speech engendered hope among the people.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2075,7 +2111,9 @@
           <t xml:space="preserve"> His smile was enigmatic and unreadable.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2106,7 +2144,9 @@
           <t xml:space="preserve"> Discounts are used to entice customers.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2137,7 +2177,9 @@
           <t xml:space="preserve"> The teacher enumerated the exam rules.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2168,7 +2210,9 @@
           <t xml:space="preserve"> His attendance was erratic throughout the term.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2199,7 +2243,9 @@
           <t xml:space="preserve"> The theory is too esoteric for beginners.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2230,7 +2276,9 @@
           <t xml:space="preserve"> Her career exemplifies success through hard work.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2261,7 +2309,9 @@
           <t xml:space="preserve"> The rent prices in the city are exorbitant.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2292,7 +2342,9 @@
           <t xml:space="preserve"> He completed the task in an expeditious manner.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2323,7 +2375,9 @@
           <t xml:space="preserve"> The argument was fallacious and weak.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2354,7 +2408,9 @@
           <t xml:space="preserve"> Your plan is feasible with enough funding.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2385,7 +2441,9 @@
           <t xml:space="preserve"> She is a fervent supporter of education for all.</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="990">
   <si>
     <t>srno</t>
   </si>
@@ -974,262 +974,262 @@
     <t xml:space="preserve"> He is a formidable opponent in debate.</t>
   </si>
   <si>
+    <t xml:space="preserve"> Frivolous </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> not serious or sensible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> trivial, silly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> serious, important </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stop spending money on frivolous things.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Futile </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> incapable of producing results </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> useless, pointless </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> effective, successful </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Their efforts to save the tree were futile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Garrulous </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> excessively talkative </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> talkative, chatty </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> silent, quiet </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The garrulous man dominated the conversation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gaunt </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> extremely thin </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> skinny, emaciated </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> healthy, plump </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> After the illness, he looked gaunt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gregarious </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sociable and outgoing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sociable, friendly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> shy, introverted </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> She is gregarious and loves meeting new people.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hackneyed </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> overused and unoriginal </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> clichéd, stale </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fresh, original </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> His speech was full of hackneyed phrases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Haphazard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> lacking order or planning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> random, chaotic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> organized, systematic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Books were arranged in a haphazard way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Haughty </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> arrogantly superior </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> arrogant, proud </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> humble, modest </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> His haughty behavior annoyed everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Heinous </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> extremely wicked or shocking </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> atrocious, evil </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> minor, trivial </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The court punished him for the heinous crime.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Idiosyncratic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> peculiar to an individual </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> peculiar, distinctive </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> common, ordinary </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> His idiosyncratic behavior made him unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Illicit </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> illegal or forbidden </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> illegal, unlawful </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> legal, lawful </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The police cracked down on illicit trade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Immaculate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> perfectly clean or pure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> spotless, flawless </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dirty, flawed </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The room was immaculate after cleaning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Imminent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> about to happen </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> impending, approaching </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> distant, remote </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A storm is imminent according to the forecast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Immutable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> unchanging over time </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fixed, unchangeable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> alterable, flexible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Moral principles should be immutable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Impartial </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> not taking sides </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> neutral, unbiased </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> biased, partial </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Judges must remain impartial in court.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Impeccable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> perfect and without mistakes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> flawless, perfect </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> faulty, imperfect </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Her pronunciation was impeccable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Impetuous </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> acting without thinking </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> rash, hasty </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cautious, careful </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> His impetuous decision caused problems.</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Frivolous </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> not serious or sensible </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> trivial, silly </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> serious, important </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Stop spending money on frivolous things.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Futile </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> incapable of producing results </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> useless, pointless </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> effective, successful </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Their efforts to save the tree were futile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Garrulous </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> excessively talkative </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> talkative, chatty </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> silent, quiet </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The garrulous man dominated the conversation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gaunt </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> extremely thin </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> skinny, emaciated </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> healthy, plump </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> After the illness, he looked gaunt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gregarious </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> sociable and outgoing </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> sociable, friendly </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> shy, introverted </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> She is gregarious and loves meeting new people.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hackneyed </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> overused and unoriginal </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> clichéd, stale </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fresh, original </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> His speech was full of hackneyed phrases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Haphazard </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> lacking order or planning </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> random, chaotic </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> organized, systematic </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Books were arranged in a haphazard way.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Haughty </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> arrogantly superior </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> arrogant, proud </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> humble, modest </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> His haughty behavior annoyed everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Heinous </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> extremely wicked or shocking </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> atrocious, evil </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> minor, trivial </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The court punished him for the heinous crime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Idiosyncratic </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> peculiar to an individual </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> peculiar, distinctive </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> common, ordinary </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> His idiosyncratic behavior made him unique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Illicit </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> illegal or forbidden </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> illegal, unlawful </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> legal, lawful </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The police cracked down on illicit trade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Immaculate </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> perfectly clean or pure </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> spotless, flawless </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> dirty, flawed </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The room was immaculate after cleaning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Imminent </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> about to happen </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> impending, approaching </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> distant, remote </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A storm is imminent according to the forecast.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Immutable </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> unchanging over time </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fixed, unchangeable </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> alterable, flexible </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Moral principles should be immutable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Impartial </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> not taking sides </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> neutral, unbiased </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> biased, partial </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Judges must remain impartial in court.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Impeccable </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> perfect and without mistakes </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> flawless, perfect </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> faulty, imperfect </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Her pronunciation was impeccable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Impetuous </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> acting without thinking </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> rash, hasty </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> cautious, careful </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> His impetuous decision caused problems.</t>
   </si>
   <si>
     <t xml:space="preserve"> Implicit </t>
@@ -3992,6 +3992,9 @@
   <sheetPr/>
   <dimension ref="A1:G201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="6" max="6" width="48" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
@@ -5438,8 +5441,8 @@
       <c r="F63" t="s">
         <v>314</v>
       </c>
-      <c r="G63" t="s">
-        <v>315</v>
+      <c r="G63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5447,367 +5450,322 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>315</v>
+      </c>
+      <c r="C64" t="s">
         <v>316</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>317</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>318</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>319</v>
       </c>
-      <c r="F64" t="s">
-        <v>320</v>
-      </c>
-      <c r="G64" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>320</v>
+      </c>
+      <c r="C65" t="s">
         <v>321</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>322</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>323</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>324</v>
       </c>
-      <c r="F65" t="s">
-        <v>325</v>
-      </c>
-      <c r="G65" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>325</v>
+      </c>
+      <c r="C66" t="s">
         <v>326</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>327</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>328</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>329</v>
       </c>
-      <c r="F66" t="s">
-        <v>330</v>
-      </c>
-      <c r="G66" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>330</v>
+      </c>
+      <c r="C67" t="s">
         <v>331</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>332</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>333</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>334</v>
       </c>
-      <c r="F67" t="s">
-        <v>335</v>
-      </c>
-      <c r="G67" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>335</v>
+      </c>
+      <c r="C68" t="s">
         <v>336</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>337</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>338</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>339</v>
       </c>
-      <c r="F68" t="s">
-        <v>340</v>
-      </c>
-      <c r="G68" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>340</v>
+      </c>
+      <c r="C69" t="s">
         <v>341</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>342</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>343</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>344</v>
       </c>
-      <c r="F69" t="s">
-        <v>345</v>
-      </c>
-      <c r="G69" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>345</v>
+      </c>
+      <c r="C70" t="s">
         <v>346</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>347</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>348</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>349</v>
       </c>
-      <c r="F70" t="s">
-        <v>350</v>
-      </c>
-      <c r="G70" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>350</v>
+      </c>
+      <c r="C71" t="s">
         <v>351</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>352</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>353</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>354</v>
       </c>
-      <c r="F71" t="s">
-        <v>355</v>
-      </c>
-      <c r="G71" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>355</v>
+      </c>
+      <c r="C72" t="s">
         <v>356</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>357</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>358</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>359</v>
       </c>
-      <c r="F72" t="s">
-        <v>360</v>
-      </c>
-      <c r="G72" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>360</v>
+      </c>
+      <c r="C73" t="s">
         <v>361</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>362</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>363</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>364</v>
       </c>
-      <c r="F73" t="s">
-        <v>365</v>
-      </c>
-      <c r="G73" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" t="s">
         <v>366</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>367</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>368</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>369</v>
       </c>
-      <c r="F74" t="s">
-        <v>370</v>
-      </c>
-      <c r="G74" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>370</v>
+      </c>
+      <c r="C75" t="s">
         <v>371</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>372</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>373</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>374</v>
       </c>
-      <c r="F75" t="s">
-        <v>375</v>
-      </c>
-      <c r="G75" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>375</v>
+      </c>
+      <c r="C76" t="s">
         <v>376</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>377</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>378</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>379</v>
       </c>
-      <c r="F76" t="s">
-        <v>380</v>
-      </c>
-      <c r="G76" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>380</v>
+      </c>
+      <c r="C77" t="s">
         <v>381</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>382</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>383</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>384</v>
       </c>
-      <c r="F77" t="s">
-        <v>385</v>
-      </c>
-      <c r="G77" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>385</v>
+      </c>
+      <c r="C78" t="s">
         <v>386</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>387</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>388</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>389</v>
       </c>
-      <c r="F78" t="s">
-        <v>390</v>
-      </c>
-      <c r="G78" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>390</v>
+      </c>
+      <c r="C79" t="s">
         <v>391</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>392</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>393</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>394</v>
-      </c>
-      <c r="F79" t="s">
-        <v>395</v>
-      </c>
-      <c r="G79" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5815,22 +5773,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>395</v>
+      </c>
+      <c r="C80" t="s">
         <v>396</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>397</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>398</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>399</v>
       </c>
-      <c r="F80" t="s">
-        <v>400</v>
-      </c>
       <c r="G80" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5853,7 +5811,7 @@
         <v>405</v>
       </c>
       <c r="G81" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -5876,7 +5834,7 @@
         <v>410</v>
       </c>
       <c r="G82" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -5899,7 +5857,7 @@
         <v>415</v>
       </c>
       <c r="G83" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -5922,7 +5880,7 @@
         <v>420</v>
       </c>
       <c r="G84" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -5945,7 +5903,7 @@
         <v>425</v>
       </c>
       <c r="G85" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -5968,7 +5926,7 @@
         <v>430</v>
       </c>
       <c r="G86" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -5991,7 +5949,7 @@
         <v>435</v>
       </c>
       <c r="G87" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6014,7 +5972,7 @@
         <v>440</v>
       </c>
       <c r="G88" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6037,7 +5995,7 @@
         <v>445</v>
       </c>
       <c r="G89" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6060,7 +6018,7 @@
         <v>450</v>
       </c>
       <c r="G90" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6083,7 +6041,7 @@
         <v>455</v>
       </c>
       <c r="G91" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6106,7 +6064,7 @@
         <v>460</v>
       </c>
       <c r="G92" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6129,7 +6087,7 @@
         <v>465</v>
       </c>
       <c r="G93" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6152,7 +6110,7 @@
         <v>470</v>
       </c>
       <c r="G94" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6175,7 +6133,7 @@
         <v>475</v>
       </c>
       <c r="G95" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6198,7 +6156,7 @@
         <v>480</v>
       </c>
       <c r="G96" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6221,7 +6179,7 @@
         <v>485</v>
       </c>
       <c r="G97" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6244,7 +6202,7 @@
         <v>490</v>
       </c>
       <c r="G98" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6267,7 +6225,7 @@
         <v>495</v>
       </c>
       <c r="G99" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6290,7 +6248,7 @@
         <v>500</v>
       </c>
       <c r="G100" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6313,7 +6271,7 @@
         <v>505</v>
       </c>
       <c r="G101" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6336,7 +6294,7 @@
         <v>509</v>
       </c>
       <c r="G102" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6359,7 +6317,7 @@
         <v>514</v>
       </c>
       <c r="G103" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6382,7 +6340,7 @@
         <v>519</v>
       </c>
       <c r="G104" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6405,7 +6363,7 @@
         <v>524</v>
       </c>
       <c r="G105" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6428,7 +6386,7 @@
         <v>529</v>
       </c>
       <c r="G106" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6451,7 +6409,7 @@
         <v>534</v>
       </c>
       <c r="G107" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6474,7 +6432,7 @@
         <v>539</v>
       </c>
       <c r="G108" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6497,7 +6455,7 @@
         <v>544</v>
       </c>
       <c r="G109" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6520,7 +6478,7 @@
         <v>549</v>
       </c>
       <c r="G110" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -6543,7 +6501,7 @@
         <v>554</v>
       </c>
       <c r="G111" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6560,13 +6518,13 @@
         <v>557</v>
       </c>
       <c r="E112" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F112" t="s">
         <v>558</v>
       </c>
       <c r="G112" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6589,7 +6547,7 @@
         <v>563</v>
       </c>
       <c r="G113" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6612,7 +6570,7 @@
         <v>568</v>
       </c>
       <c r="G114" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6635,7 +6593,7 @@
         <v>573</v>
       </c>
       <c r="G115" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6658,7 +6616,7 @@
         <v>577</v>
       </c>
       <c r="G116" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6681,7 +6639,7 @@
         <v>582</v>
       </c>
       <c r="G117" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6704,7 +6662,7 @@
         <v>587</v>
       </c>
       <c r="G118" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6727,7 +6685,7 @@
         <v>592</v>
       </c>
       <c r="G119" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6750,7 +6708,7 @@
         <v>597</v>
       </c>
       <c r="G120" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6773,7 +6731,7 @@
         <v>602</v>
       </c>
       <c r="G121" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6796,7 +6754,7 @@
         <v>607</v>
       </c>
       <c r="G122" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6819,7 +6777,7 @@
         <v>612</v>
       </c>
       <c r="G123" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6842,7 +6800,7 @@
         <v>617</v>
       </c>
       <c r="G124" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6865,7 +6823,7 @@
         <v>622</v>
       </c>
       <c r="G125" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6888,7 +6846,7 @@
         <v>627</v>
       </c>
       <c r="G126" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6911,7 +6869,7 @@
         <v>632</v>
       </c>
       <c r="G127" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6934,7 +6892,7 @@
         <v>637</v>
       </c>
       <c r="G128" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6957,7 +6915,7 @@
         <v>642</v>
       </c>
       <c r="G129" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6980,7 +6938,7 @@
         <v>647</v>
       </c>
       <c r="G130" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -7003,7 +6961,7 @@
         <v>652</v>
       </c>
       <c r="G131" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7026,7 +6984,7 @@
         <v>657</v>
       </c>
       <c r="G132" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -7049,7 +7007,7 @@
         <v>662</v>
       </c>
       <c r="G133" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7072,7 +7030,7 @@
         <v>667</v>
       </c>
       <c r="G134" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7095,7 +7053,7 @@
         <v>672</v>
       </c>
       <c r="G135" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7118,7 +7076,7 @@
         <v>677</v>
       </c>
       <c r="G136" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7141,7 +7099,7 @@
         <v>682</v>
       </c>
       <c r="G137" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7164,7 +7122,7 @@
         <v>687</v>
       </c>
       <c r="G138" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7187,7 +7145,7 @@
         <v>692</v>
       </c>
       <c r="G139" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7210,7 +7168,7 @@
         <v>697</v>
       </c>
       <c r="G140" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7233,7 +7191,7 @@
         <v>702</v>
       </c>
       <c r="G141" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7256,7 +7214,7 @@
         <v>707</v>
       </c>
       <c r="G142" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7279,7 +7237,7 @@
         <v>712</v>
       </c>
       <c r="G143" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7302,7 +7260,7 @@
         <v>717</v>
       </c>
       <c r="G144" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -7325,7 +7283,7 @@
         <v>722</v>
       </c>
       <c r="G145" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -7348,7 +7306,7 @@
         <v>727</v>
       </c>
       <c r="G146" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -7371,7 +7329,7 @@
         <v>732</v>
       </c>
       <c r="G147" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -7394,7 +7352,7 @@
         <v>737</v>
       </c>
       <c r="G148" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -7417,7 +7375,7 @@
         <v>742</v>
       </c>
       <c r="G149" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -7440,7 +7398,7 @@
         <v>747</v>
       </c>
       <c r="G150" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -7463,7 +7421,7 @@
         <v>752</v>
       </c>
       <c r="G151" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -7486,7 +7444,7 @@
         <v>757</v>
       </c>
       <c r="G152" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -7509,7 +7467,7 @@
         <v>762</v>
       </c>
       <c r="G153" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -7532,7 +7490,7 @@
         <v>767</v>
       </c>
       <c r="G154" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -7555,7 +7513,7 @@
         <v>772</v>
       </c>
       <c r="G155" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -7578,7 +7536,7 @@
         <v>776</v>
       </c>
       <c r="G156" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -7601,7 +7559,7 @@
         <v>781</v>
       </c>
       <c r="G157" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -7624,7 +7582,7 @@
         <v>786</v>
       </c>
       <c r="G158" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -7647,7 +7605,7 @@
         <v>791</v>
       </c>
       <c r="G159" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -7670,7 +7628,7 @@
         <v>796</v>
       </c>
       <c r="G160" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7693,7 +7651,7 @@
         <v>801</v>
       </c>
       <c r="G161" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7716,7 +7674,7 @@
         <v>806</v>
       </c>
       <c r="G162" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7739,7 +7697,7 @@
         <v>810</v>
       </c>
       <c r="G163" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7762,7 +7720,7 @@
         <v>815</v>
       </c>
       <c r="G164" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7785,7 +7743,7 @@
         <v>818</v>
       </c>
       <c r="G165" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7808,7 +7766,7 @@
         <v>823</v>
       </c>
       <c r="G166" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7831,7 +7789,7 @@
         <v>828</v>
       </c>
       <c r="G167" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7854,7 +7812,7 @@
         <v>833</v>
       </c>
       <c r="G168" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7877,7 +7835,7 @@
         <v>838</v>
       </c>
       <c r="G169" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7900,7 +7858,7 @@
         <v>843</v>
       </c>
       <c r="G170" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7923,7 +7881,7 @@
         <v>848</v>
       </c>
       <c r="G171" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7946,7 +7904,7 @@
         <v>852</v>
       </c>
       <c r="G172" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7969,7 +7927,7 @@
         <v>857</v>
       </c>
       <c r="G173" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7992,7 +7950,7 @@
         <v>862</v>
       </c>
       <c r="G174" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -8015,7 +7973,7 @@
         <v>867</v>
       </c>
       <c r="G175" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -8038,7 +7996,7 @@
         <v>872</v>
       </c>
       <c r="G176" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -8061,7 +8019,7 @@
         <v>876</v>
       </c>
       <c r="G177" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -8084,7 +8042,7 @@
         <v>881</v>
       </c>
       <c r="G178" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -8107,7 +8065,7 @@
         <v>886</v>
       </c>
       <c r="G179" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -8130,7 +8088,7 @@
         <v>891</v>
       </c>
       <c r="G180" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -8153,7 +8111,7 @@
         <v>896</v>
       </c>
       <c r="G181" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -8176,7 +8134,7 @@
         <v>901</v>
       </c>
       <c r="G182" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -8199,7 +8157,7 @@
         <v>906</v>
       </c>
       <c r="G183" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -8222,7 +8180,7 @@
         <v>911</v>
       </c>
       <c r="G184" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -8239,13 +8197,13 @@
         <v>914</v>
       </c>
       <c r="E185" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F185" t="s">
         <v>915</v>
       </c>
       <c r="G185" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -8268,7 +8226,7 @@
         <v>920</v>
       </c>
       <c r="G186" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -8291,7 +8249,7 @@
         <v>925</v>
       </c>
       <c r="G187" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -8314,7 +8272,7 @@
         <v>929</v>
       </c>
       <c r="G188" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -8337,7 +8295,7 @@
         <v>933</v>
       </c>
       <c r="G189" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8360,7 +8318,7 @@
         <v>938</v>
       </c>
       <c r="G190" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8383,7 +8341,7 @@
         <v>942</v>
       </c>
       <c r="G191" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8406,7 +8364,7 @@
         <v>947</v>
       </c>
       <c r="G192" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8429,7 +8387,7 @@
         <v>952</v>
       </c>
       <c r="G193" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8452,7 +8410,7 @@
         <v>957</v>
       </c>
       <c r="G194" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8475,7 +8433,7 @@
         <v>961</v>
       </c>
       <c r="G195" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8489,7 +8447,7 @@
         <v>963</v>
       </c>
       <c r="D196" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E196" t="s">
         <v>170</v>
@@ -8498,7 +8456,7 @@
         <v>964</v>
       </c>
       <c r="G196" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8521,7 +8479,7 @@
         <v>969</v>
       </c>
       <c r="G197" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8544,7 +8502,7 @@
         <v>974</v>
       </c>
       <c r="G198" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8567,7 +8525,7 @@
         <v>979</v>
       </c>
       <c r="G199" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8590,7 +8548,7 @@
         <v>984</v>
       </c>
       <c r="G200" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8613,7 +8571,7 @@
         <v>989</v>
       </c>
       <c r="G201" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3009,7 +3009,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3020,13 +3020,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3494,28 +3487,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3524,118 +3520,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5468,7 +5461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5486,6 +5479,9 @@
       </c>
       <c r="F65" t="s">
         <v>324</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:6">

--- a/UserScore/wordoftheday.xlsx
+++ b/UserScore/wordoftheday.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="990">
   <si>
     <t>srno</t>
   </si>
@@ -1064,6 +1064,9 @@
     <t xml:space="preserve"> His speech was full of hackneyed phrases.</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t xml:space="preserve"> Haphazard </t>
   </si>
   <si>
@@ -1227,9 +1230,6 @@
   </si>
   <si>
     <t xml:space="preserve"> His impetuous decision caused problems.</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t xml:space="preserve"> Implicit </t>
@@ -3009,7 +3009,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3020,6 +3020,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3487,31 +3494,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3520,115 +3524,118 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3985,9 +3992,6 @@
   <sheetPr/>
   <dimension ref="A1:G201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
-  <cols>
-    <col min="6" max="6" width="48" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
@@ -5484,7 +5488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5503,8 +5507,11 @@
       <c r="F66" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5523,8 +5530,11 @@
       <c r="F67" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5543,8 +5553,11 @@
       <c r="F68" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5563,205 +5576,238 @@
       <c r="F69" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C70" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D70" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E70" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F70" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>350</v>
+      </c>
+      <c r="G70" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C71" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D71" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E71" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F71" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>355</v>
+      </c>
+      <c r="G71" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C72" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D72" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F72" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>360</v>
+      </c>
+      <c r="G72" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C73" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D73" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E73" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F73" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>365</v>
+      </c>
+      <c r="G73" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C74" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D74" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E74" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F74" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>370</v>
+      </c>
+      <c r="G74" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C75" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D75" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F75" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>375</v>
+      </c>
+      <c r="G75" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C76" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D76" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E76" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F76" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>380</v>
+      </c>
+      <c r="G76" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C77" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D77" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E77" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F77" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>385</v>
+      </c>
+      <c r="G77" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C78" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D78" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E78" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F78" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>390</v>
+      </c>
+      <c r="G78" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C79" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D79" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E79" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F79" t="s">
-        <v>394</v>
+        <v>395</v>
+      </c>
+      <c r="G79" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5769,22 +5815,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C80" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D80" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E80" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F80" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G80" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5807,7 +5853,7 @@
         <v>405</v>
       </c>
       <c r="G81" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -5830,7 +5876,7 @@
         <v>410</v>
       </c>
       <c r="G82" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -5853,7 +5899,7 @@
         <v>415</v>
       </c>
       <c r="G83" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -5876,7 +5922,7 @@
         <v>420</v>
       </c>
       <c r="G84" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -5899,7 +5945,7 @@
         <v>425</v>
       </c>
       <c r="G85" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -5922,7 +5968,7 @@
         <v>430</v>
       </c>
       <c r="G86" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -5945,7 +5991,7 @@
         <v>435</v>
       </c>
       <c r="G87" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5968,7 +6014,7 @@
         <v>440</v>
       </c>
       <c r="G88" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -5991,7 +6037,7 @@
         <v>445</v>
       </c>
       <c r="G89" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6014,7 +6060,7 @@
         <v>450</v>
       </c>
       <c r="G90" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6037,7 +6083,7 @@
         <v>455</v>
       </c>
       <c r="G91" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6060,7 +6106,7 @@
         <v>460</v>
       </c>
       <c r="G92" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6083,7 +6129,7 @@
         <v>465</v>
       </c>
       <c r="G93" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6106,7 +6152,7 @@
         <v>470</v>
       </c>
       <c r="G94" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6129,7 +6175,7 @@
         <v>475</v>
       </c>
       <c r="G95" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6152,7 +6198,7 @@
         <v>480</v>
       </c>
       <c r="G96" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6175,7 +6221,7 @@
         <v>485</v>
       </c>
       <c r="G97" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6198,7 +6244,7 @@
         <v>490</v>
       </c>
       <c r="G98" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6221,7 +6267,7 @@
         <v>495</v>
       </c>
       <c r="G99" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6244,7 +6290,7 @@
         <v>500</v>
       </c>
       <c r="G100" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6267,7 +6313,7 @@
         <v>505</v>
       </c>
       <c r="G101" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6290,7 +6336,7 @@
         <v>509</v>
       </c>
       <c r="G102" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6313,7 +6359,7 @@
         <v>514</v>
       </c>
       <c r="G103" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6336,7 +6382,7 @@
         <v>519</v>
       </c>
       <c r="G104" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6359,7 +6405,7 @@
         <v>524</v>
       </c>
       <c r="G105" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6382,7 +6428,7 @@
         <v>529</v>
       </c>
       <c r="G106" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6405,7 +6451,7 @@
         <v>534</v>
       </c>
       <c r="G107" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6428,7 +6474,7 @@
         <v>539</v>
       </c>
       <c r="G108" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6451,7 +6497,7 @@
         <v>544</v>
       </c>
       <c r="G109" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6474,7 +6520,7 @@
         <v>549</v>
       </c>
       <c r="G110" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -6497,7 +6543,7 @@
         <v>554</v>
       </c>
       <c r="G111" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6514,13 +6560,13 @@
         <v>557</v>
       </c>
       <c r="E112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F112" t="s">
         <v>558</v>
       </c>
       <c r="G112" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6543,7 +6589,7 @@
         <v>563</v>
       </c>
       <c r="G113" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6566,7 +6612,7 @@
         <v>568</v>
       </c>
       <c r="G114" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6589,7 +6635,7 @@
         <v>573</v>
       </c>
       <c r="G115" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6612,7 +6658,7 @@
         <v>577</v>
       </c>
       <c r="G116" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6635,7 +6681,7 @@
         <v>582</v>
       </c>
       <c r="G117" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6658,7 +6704,7 @@
         <v>587</v>
       </c>
       <c r="G118" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6681,7 +6727,7 @@
         <v>592</v>
       </c>
       <c r="G119" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6704,7 +6750,7 @@
         <v>597</v>
       </c>
       <c r="G120" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6727,7 +6773,7 @@
         <v>602</v>
       </c>
       <c r="G121" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6750,7 +6796,7 @@
         <v>607</v>
       </c>
       <c r="G122" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6773,7 +6819,7 @@
         <v>612</v>
       </c>
       <c r="G123" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6796,7 +6842,7 @@
         <v>617</v>
       </c>
       <c r="G124" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6819,7 +6865,7 @@
         <v>622</v>
       </c>
       <c r="G125" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6842,7 +6888,7 @@
         <v>627</v>
       </c>
       <c r="G126" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6865,7 +6911,7 @@
         <v>632</v>
       </c>
       <c r="G127" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6888,7 +6934,7 @@
         <v>637</v>
       </c>
       <c r="G128" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6911,7 +6957,7 @@
         <v>642</v>
       </c>
       <c r="G129" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6934,7 +6980,7 @@
         <v>647</v>
       </c>
       <c r="G130" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6957,7 +7003,7 @@
         <v>652</v>
       </c>
       <c r="G131" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6980,7 +7026,7 @@
         <v>657</v>
       </c>
       <c r="G132" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -7003,7 +7049,7 @@
         <v>662</v>
       </c>
       <c r="G133" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7026,7 +7072,7 @@
         <v>667</v>
       </c>
       <c r="G134" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7049,7 +7095,7 @@
         <v>672</v>
       </c>
       <c r="G135" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7072,7 +7118,7 @@
         <v>677</v>
       </c>
       <c r="G136" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7095,7 +7141,7 @@
         <v>682</v>
       </c>
       <c r="G137" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7118,7 +7164,7 @@
         <v>687</v>
       </c>
       <c r="G138" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7141,7 +7187,7 @@
         <v>692</v>
       </c>
       <c r="G139" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7164,7 +7210,7 @@
         <v>697</v>
       </c>
       <c r="G140" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7187,7 +7233,7 @@
         <v>702</v>
       </c>
       <c r="G141" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7210,7 +7256,7 @@
         <v>707</v>
       </c>
       <c r="G142" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7233,7 +7279,7 @@
         <v>712</v>
       </c>
       <c r="G143" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7256,7 +7302,7 @@
         <v>717</v>
       </c>
       <c r="G144" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -7279,7 +7325,7 @@
         <v>722</v>
       </c>
       <c r="G145" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -7302,7 +7348,7 @@
         <v>727</v>
       </c>
       <c r="G146" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -7325,7 +7371,7 @@
         <v>732</v>
       </c>
       <c r="G147" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -7348,7 +7394,7 @@
         <v>737</v>
       </c>
       <c r="G148" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -7371,7 +7417,7 @@
         <v>742</v>
       </c>
       <c r="G149" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -7394,7 +7440,7 @@
         <v>747</v>
       </c>
       <c r="G150" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -7417,7 +7463,7 @@
         <v>752</v>
       </c>
       <c r="G151" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -7440,7 +7486,7 @@
         <v>757</v>
       </c>
       <c r="G152" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -7463,7 +7509,7 @@
         <v>762</v>
       </c>
       <c r="G153" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -7486,7 +7532,7 @@
         <v>767</v>
       </c>
       <c r="G154" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -7509,7 +7555,7 @@
         <v>772</v>
       </c>
       <c r="G155" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -7532,7 +7578,7 @@
         <v>776</v>
       </c>
       <c r="G156" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -7555,7 +7601,7 @@
         <v>781</v>
       </c>
       <c r="G157" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -7578,7 +7624,7 @@
         <v>786</v>
       </c>
       <c r="G158" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -7601,7 +7647,7 @@
         <v>791</v>
       </c>
       <c r="G159" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -7624,7 +7670,7 @@
         <v>796</v>
       </c>
       <c r="G160" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7647,7 +7693,7 @@
         <v>801</v>
       </c>
       <c r="G161" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7670,7 +7716,7 @@
         <v>806</v>
       </c>
       <c r="G162" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7693,7 +7739,7 @@
         <v>810</v>
       </c>
       <c r="G163" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7716,7 +7762,7 @@
         <v>815</v>
       </c>
       <c r="G164" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7739,7 +7785,7 @@
         <v>818</v>
       </c>
       <c r="G165" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7762,7 +7808,7 @@
         <v>823</v>
       </c>
       <c r="G166" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7785,7 +7831,7 @@
         <v>828</v>
       </c>
       <c r="G167" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7808,7 +7854,7 @@
         <v>833</v>
       </c>
       <c r="G168" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7831,7 +7877,7 @@
         <v>838</v>
       </c>
       <c r="G169" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7854,7 +7900,7 @@
         <v>843</v>
       </c>
       <c r="G170" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7877,7 +7923,7 @@
         <v>848</v>
       </c>
       <c r="G171" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7900,7 +7946,7 @@
         <v>852</v>
       </c>
       <c r="G172" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7923,7 +7969,7 @@
         <v>857</v>
       </c>
       <c r="G173" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7946,7 +7992,7 @@
         <v>862</v>
       </c>
       <c r="G174" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7969,7 +8015,7 @@
         <v>867</v>
       </c>
       <c r="G175" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7992,7 +8038,7 @@
         <v>872</v>
       </c>
       <c r="G176" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -8015,7 +8061,7 @@
         <v>876</v>
       </c>
       <c r="G177" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -8038,7 +8084,7 @@
         <v>881</v>
       </c>
       <c r="G178" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -8061,7 +8107,7 @@
         <v>886</v>
       </c>
       <c r="G179" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -8084,7 +8130,7 @@
         <v>891</v>
       </c>
       <c r="G180" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -8107,7 +8153,7 @@
         <v>896</v>
       </c>
       <c r="G181" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -8130,7 +8176,7 @@
         <v>901</v>
       </c>
       <c r="G182" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -8153,7 +8199,7 @@
         <v>906</v>
       </c>
       <c r="G183" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -8176,7 +8222,7 @@
         <v>911</v>
       </c>
       <c r="G184" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -8193,13 +8239,13 @@
         <v>914</v>
       </c>
       <c r="E185" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F185" t="s">
         <v>915</v>
       </c>
       <c r="G185" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -8222,7 +8268,7 @@
         <v>920</v>
       </c>
       <c r="G186" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -8245,7 +8291,7 @@
         <v>925</v>
       </c>
       <c r="G187" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -8268,7 +8314,7 @@
         <v>929</v>
       </c>
       <c r="G188" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -8291,7 +8337,7 @@
         <v>933</v>
       </c>
       <c r="G189" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8314,7 +8360,7 @@
         <v>938</v>
       </c>
       <c r="G190" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8337,7 +8383,7 @@
         <v>942</v>
       </c>
       <c r="G191" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8360,7 +8406,7 @@
         <v>947</v>
       </c>
       <c r="G192" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8383,7 +8429,7 @@
         <v>952</v>
       </c>
       <c r="G193" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8406,7 +8452,7 @@
         <v>957</v>
       </c>
       <c r="G194" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8429,7 +8475,7 @@
         <v>961</v>
       </c>
       <c r="G195" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8443,7 +8489,7 @@
         <v>963</v>
       </c>
       <c r="D196" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E196" t="s">
         <v>170</v>
@@ -8452,7 +8498,7 @@
         <v>964</v>
       </c>
       <c r="G196" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8475,7 +8521,7 @@
         <v>969</v>
       </c>
       <c r="G197" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8498,7 +8544,7 @@
         <v>974</v>
       </c>
       <c r="G198" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8521,7 +8567,7 @@
         <v>979</v>
       </c>
       <c r="G199" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8544,7 +8590,7 @@
         <v>984</v>
       </c>
       <c r="G200" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8567,7 +8613,7 @@
         <v>989</v>
       </c>
       <c r="G201" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
